--- a/backend/templates/pr-template 4p.xlsx
+++ b/backend/templates/pr-template 4p.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FAC2BE-2A6D-4C5B-AFEC-BC28FDDB01B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9253B3F1-3C9D-4413-BC3E-17AB9B9B72A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -409,7 +409,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -514,18 +514,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -538,9 +526,71 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
@@ -562,12 +612,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -607,64 +651,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1085,26 +1082,26 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="72"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="54"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="75"/>
+      <c r="A2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="78"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="60"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1112,1270 +1109,1270 @@
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="27"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="80"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="62"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="82"/>
+      <c r="B5" s="64"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="83" t="s">
+      <c r="E5" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="84"/>
+      <c r="F5" s="66"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="87"/>
-      <c r="B6" s="88"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="48"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="85" t="s">
+      <c r="E6" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="86"/>
+      <c r="F6" s="46"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="89" t="s">
+      <c r="A7" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="56" t="s">
+      <c r="D7" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="56" t="s">
+      <c r="E7" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="56" t="s">
+      <c r="F7" s="51" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="90"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
+      <c r="A8" s="50"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="46"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="48"/>
+      <c r="A9" s="42"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="87"/>
       <c r="F9" s="39">
         <f t="shared" ref="F9:F72" si="0">D9*E9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="46"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="48"/>
+      <c r="A10" s="42"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="87"/>
       <c r="F10" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="46"/>
-      <c r="B11" s="47"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="48"/>
+      <c r="A11" s="42"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="87"/>
       <c r="F11" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="46"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="48"/>
+      <c r="A12" s="42"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="87"/>
       <c r="F12" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="46"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="48"/>
+      <c r="A13" s="42"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="87"/>
       <c r="F13" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="46"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="48"/>
+      <c r="A14" s="42"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="87"/>
       <c r="F14" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="46"/>
-      <c r="B15" s="47"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="48"/>
+      <c r="A15" s="42"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="87"/>
       <c r="F15" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="46"/>
-      <c r="B16" s="47"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="48"/>
+      <c r="A16" s="42"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="87"/>
       <c r="F16" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="46"/>
-      <c r="B17" s="47"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="48"/>
+      <c r="A17" s="42"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="87"/>
       <c r="F17" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="46"/>
-      <c r="B18" s="47"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="48"/>
+      <c r="A18" s="42"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="87"/>
       <c r="F18" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="46"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="48"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="87"/>
       <c r="F19" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="46"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="48"/>
+      <c r="A20" s="42"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="87"/>
       <c r="F20" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="46"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="48"/>
+      <c r="A21" s="42"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="87"/>
       <c r="F21" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="46"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="48"/>
+      <c r="A22" s="42"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="87"/>
       <c r="F22" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="46"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="48"/>
+      <c r="A23" s="42"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="87"/>
       <c r="F23" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="46"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="48"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="87"/>
       <c r="F24" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="46"/>
-      <c r="B25" s="47"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="48"/>
+      <c r="A25" s="42"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="87"/>
       <c r="F25" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="46"/>
-      <c r="B26" s="47"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="48"/>
+      <c r="A26" s="42"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="87"/>
       <c r="F26" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="46"/>
-      <c r="B27" s="47"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="48"/>
+      <c r="A27" s="42"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="87"/>
       <c r="F27" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="46"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="48"/>
+      <c r="A28" s="42"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="87"/>
       <c r="F28" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="46"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="48"/>
+      <c r="A29" s="42"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="87"/>
       <c r="F29" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="46"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="48"/>
+      <c r="A30" s="42"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="87"/>
       <c r="F30" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="46"/>
-      <c r="B31" s="47"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="48"/>
+      <c r="A31" s="42"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="87"/>
       <c r="F31" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="46"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="48"/>
+      <c r="A32" s="42"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="87"/>
       <c r="F32" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="46"/>
-      <c r="B33" s="47"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="48"/>
+      <c r="A33" s="42"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="87"/>
       <c r="F33" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="46"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="48"/>
+      <c r="A34" s="42"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="87"/>
       <c r="F34" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="46"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="48"/>
+      <c r="A35" s="42"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="87"/>
       <c r="F35" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="46"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="48"/>
+      <c r="A36" s="42"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="87"/>
       <c r="F36" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="46"/>
-      <c r="B37" s="47"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="48"/>
+      <c r="A37" s="42"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="87"/>
       <c r="F37" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="46"/>
-      <c r="B38" s="47"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="48"/>
+      <c r="A38" s="42"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="87"/>
       <c r="F38" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="46"/>
-      <c r="B39" s="47"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="48"/>
+      <c r="A39" s="42"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="87"/>
       <c r="F39" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G39" s="91" t="s">
+      <c r="G39" s="44" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="46"/>
-      <c r="B40" s="47"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="48"/>
+      <c r="A40" s="42"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="87"/>
       <c r="F40" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G40" s="91" t="s">
+      <c r="G40" s="44" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="46"/>
-      <c r="B41" s="47"/>
-      <c r="C41" s="45"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="48"/>
+      <c r="A41" s="42"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="87"/>
       <c r="F41" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="46"/>
-      <c r="B42" s="47"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="48"/>
+      <c r="A42" s="42"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="87"/>
       <c r="F42" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="46"/>
-      <c r="B43" s="47"/>
-      <c r="C43" s="45"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="48"/>
+      <c r="A43" s="42"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="87"/>
       <c r="F43" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="46"/>
-      <c r="B44" s="47"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="48"/>
+      <c r="A44" s="42"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="87"/>
       <c r="F44" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="46"/>
-      <c r="B45" s="47"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="48"/>
+      <c r="A45" s="42"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="87"/>
       <c r="F45" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="46"/>
-      <c r="B46" s="47"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="48"/>
+      <c r="A46" s="42"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="87"/>
       <c r="F46" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="46"/>
-      <c r="B47" s="47"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="48"/>
+      <c r="A47" s="42"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="87"/>
       <c r="F47" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="46"/>
-      <c r="B48" s="47"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="48"/>
+      <c r="A48" s="42"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="87"/>
       <c r="F48" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="46"/>
-      <c r="B49" s="47"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="48"/>
+      <c r="A49" s="42"/>
+      <c r="B49" s="43"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="87"/>
       <c r="F49" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="46"/>
-      <c r="B50" s="47"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="48"/>
+      <c r="A50" s="42"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="87"/>
       <c r="F50" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="46"/>
-      <c r="B51" s="47"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="48"/>
+      <c r="A51" s="42"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="87"/>
       <c r="F51" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="46"/>
-      <c r="B52" s="47"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="48"/>
+      <c r="A52" s="42"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="87"/>
       <c r="F52" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="46"/>
-      <c r="B53" s="47"/>
-      <c r="C53" s="45"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="48"/>
+      <c r="A53" s="42"/>
+      <c r="B53" s="43"/>
+      <c r="C53" s="41"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="87"/>
       <c r="F53" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="46"/>
-      <c r="B54" s="47"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="45"/>
-      <c r="E54" s="48"/>
+      <c r="A54" s="42"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="87"/>
       <c r="F54" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="46"/>
-      <c r="B55" s="47"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="48"/>
+      <c r="A55" s="42"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="41"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="87"/>
       <c r="F55" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="46"/>
-      <c r="B56" s="47"/>
-      <c r="C56" s="45"/>
-      <c r="D56" s="45"/>
-      <c r="E56" s="48"/>
+      <c r="A56" s="42"/>
+      <c r="B56" s="43"/>
+      <c r="C56" s="41"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="87"/>
       <c r="F56" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="46"/>
-      <c r="B57" s="47"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="45"/>
-      <c r="E57" s="48"/>
+      <c r="A57" s="42"/>
+      <c r="B57" s="43"/>
+      <c r="C57" s="41"/>
+      <c r="D57" s="41"/>
+      <c r="E57" s="87"/>
       <c r="F57" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="46"/>
-      <c r="B58" s="47"/>
-      <c r="C58" s="45"/>
-      <c r="D58" s="45"/>
-      <c r="E58" s="48"/>
+      <c r="A58" s="42"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="41"/>
+      <c r="E58" s="87"/>
       <c r="F58" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="46"/>
-      <c r="B59" s="47"/>
-      <c r="C59" s="45"/>
-      <c r="D59" s="45"/>
-      <c r="E59" s="48"/>
+      <c r="A59" s="42"/>
+      <c r="B59" s="43"/>
+      <c r="C59" s="41"/>
+      <c r="D59" s="41"/>
+      <c r="E59" s="87"/>
       <c r="F59" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="46"/>
-      <c r="B60" s="47"/>
-      <c r="C60" s="45"/>
-      <c r="D60" s="45"/>
-      <c r="E60" s="48"/>
+      <c r="A60" s="42"/>
+      <c r="B60" s="43"/>
+      <c r="C60" s="41"/>
+      <c r="D60" s="41"/>
+      <c r="E60" s="87"/>
       <c r="F60" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="46"/>
-      <c r="B61" s="47"/>
-      <c r="C61" s="45"/>
-      <c r="D61" s="45"/>
-      <c r="E61" s="48"/>
+      <c r="A61" s="42"/>
+      <c r="B61" s="43"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="87"/>
       <c r="F61" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="46"/>
-      <c r="B62" s="47"/>
-      <c r="C62" s="45"/>
-      <c r="D62" s="45"/>
-      <c r="E62" s="48"/>
+      <c r="A62" s="42"/>
+      <c r="B62" s="43"/>
+      <c r="C62" s="41"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="87"/>
       <c r="F62" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="46"/>
-      <c r="B63" s="47"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="48"/>
+      <c r="A63" s="42"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="87"/>
       <c r="F63" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="46"/>
-      <c r="B64" s="47"/>
-      <c r="C64" s="45"/>
-      <c r="D64" s="45"/>
-      <c r="E64" s="48"/>
+      <c r="A64" s="42"/>
+      <c r="B64" s="43"/>
+      <c r="C64" s="41"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="87"/>
       <c r="F64" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="46"/>
-      <c r="B65" s="47"/>
-      <c r="C65" s="45"/>
-      <c r="D65" s="45"/>
-      <c r="E65" s="48"/>
+      <c r="A65" s="42"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="41"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="87"/>
       <c r="F65" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="46"/>
-      <c r="B66" s="47"/>
-      <c r="C66" s="45"/>
-      <c r="D66" s="45"/>
-      <c r="E66" s="48"/>
+      <c r="A66" s="42"/>
+      <c r="B66" s="43"/>
+      <c r="C66" s="41"/>
+      <c r="D66" s="41"/>
+      <c r="E66" s="87"/>
       <c r="F66" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="46"/>
-      <c r="B67" s="47"/>
-      <c r="C67" s="45"/>
-      <c r="D67" s="45"/>
-      <c r="E67" s="48"/>
+      <c r="A67" s="42"/>
+      <c r="B67" s="43"/>
+      <c r="C67" s="41"/>
+      <c r="D67" s="41"/>
+      <c r="E67" s="87"/>
       <c r="F67" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="46"/>
-      <c r="B68" s="47"/>
-      <c r="C68" s="45"/>
-      <c r="D68" s="45"/>
-      <c r="E68" s="48"/>
+      <c r="A68" s="42"/>
+      <c r="B68" s="43"/>
+      <c r="C68" s="41"/>
+      <c r="D68" s="41"/>
+      <c r="E68" s="87"/>
       <c r="F68" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="46"/>
-      <c r="B69" s="47"/>
-      <c r="C69" s="45"/>
-      <c r="D69" s="45"/>
-      <c r="E69" s="48"/>
+      <c r="A69" s="42"/>
+      <c r="B69" s="43"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="87"/>
       <c r="F69" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="46"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="45"/>
-      <c r="D70" s="45"/>
-      <c r="E70" s="48"/>
+      <c r="A70" s="42"/>
+      <c r="B70" s="43"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="41"/>
+      <c r="E70" s="87"/>
       <c r="F70" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="46"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
-      <c r="E71" s="48"/>
+      <c r="A71" s="42"/>
+      <c r="B71" s="43"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="41"/>
+      <c r="E71" s="87"/>
       <c r="F71" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="46"/>
-      <c r="B72" s="47"/>
-      <c r="C72" s="45"/>
-      <c r="D72" s="45"/>
-      <c r="E72" s="48"/>
+      <c r="A72" s="42"/>
+      <c r="B72" s="43"/>
+      <c r="C72" s="41"/>
+      <c r="D72" s="41"/>
+      <c r="E72" s="87"/>
       <c r="F72" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="46"/>
-      <c r="B73" s="47"/>
-      <c r="C73" s="45"/>
-      <c r="D73" s="45"/>
-      <c r="E73" s="48"/>
+      <c r="A73" s="42"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="41"/>
+      <c r="D73" s="41"/>
+      <c r="E73" s="87"/>
       <c r="F73" s="39">
         <f t="shared" ref="F73:F83" si="1">D73*E73</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="46"/>
-      <c r="B74" s="47"/>
-      <c r="C74" s="45"/>
-      <c r="D74" s="45"/>
-      <c r="E74" s="48"/>
+      <c r="A74" s="42"/>
+      <c r="B74" s="43"/>
+      <c r="C74" s="41"/>
+      <c r="D74" s="41"/>
+      <c r="E74" s="87"/>
       <c r="F74" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="46"/>
-      <c r="B75" s="47"/>
-      <c r="C75" s="45"/>
-      <c r="D75" s="45"/>
-      <c r="E75" s="48"/>
+      <c r="A75" s="42"/>
+      <c r="B75" s="43"/>
+      <c r="C75" s="41"/>
+      <c r="D75" s="41"/>
+      <c r="E75" s="87"/>
       <c r="F75" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="46"/>
-      <c r="B76" s="47"/>
-      <c r="C76" s="45"/>
-      <c r="D76" s="45"/>
-      <c r="E76" s="48"/>
+      <c r="A76" s="42"/>
+      <c r="B76" s="43"/>
+      <c r="C76" s="41"/>
+      <c r="D76" s="41"/>
+      <c r="E76" s="87"/>
       <c r="F76" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="46"/>
-      <c r="B77" s="47"/>
-      <c r="C77" s="45"/>
-      <c r="D77" s="45"/>
-      <c r="E77" s="48"/>
+      <c r="A77" s="42"/>
+      <c r="B77" s="43"/>
+      <c r="C77" s="41"/>
+      <c r="D77" s="41"/>
+      <c r="E77" s="87"/>
       <c r="F77" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="46"/>
-      <c r="B78" s="47"/>
-      <c r="C78" s="45"/>
-      <c r="D78" s="45"/>
-      <c r="E78" s="48"/>
+      <c r="A78" s="42"/>
+      <c r="B78" s="43"/>
+      <c r="C78" s="41"/>
+      <c r="D78" s="41"/>
+      <c r="E78" s="87"/>
       <c r="F78" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="46"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="45"/>
-      <c r="D79" s="45"/>
-      <c r="E79" s="48"/>
+      <c r="A79" s="42"/>
+      <c r="B79" s="43"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="87"/>
       <c r="F79" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="46"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="45"/>
-      <c r="D80" s="45"/>
-      <c r="E80" s="48"/>
+      <c r="A80" s="42"/>
+      <c r="B80" s="43"/>
+      <c r="C80" s="41"/>
+      <c r="D80" s="41"/>
+      <c r="E80" s="87"/>
       <c r="F80" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G80" s="91" t="s">
+      <c r="G80" s="44" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="46"/>
-      <c r="B81" s="47"/>
-      <c r="C81" s="45"/>
-      <c r="D81" s="45"/>
-      <c r="E81" s="48"/>
+      <c r="A81" s="42"/>
+      <c r="B81" s="43"/>
+      <c r="C81" s="41"/>
+      <c r="D81" s="41"/>
+      <c r="E81" s="87"/>
       <c r="F81" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G81" s="91" t="s">
+      <c r="G81" s="44" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="46"/>
-      <c r="B82" s="47"/>
-      <c r="C82" s="45"/>
-      <c r="D82" s="45"/>
-      <c r="E82" s="48"/>
+      <c r="A82" s="42"/>
+      <c r="B82" s="43"/>
+      <c r="C82" s="41"/>
+      <c r="D82" s="41"/>
+      <c r="E82" s="87"/>
       <c r="F82" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="46"/>
-      <c r="B83" s="47"/>
-      <c r="C83" s="45"/>
-      <c r="D83" s="45"/>
-      <c r="E83" s="48"/>
+      <c r="A83" s="42"/>
+      <c r="B83" s="43"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="87"/>
       <c r="F83" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="46"/>
-      <c r="B84" s="47"/>
-      <c r="C84" s="45"/>
-      <c r="D84" s="45"/>
-      <c r="E84" s="48"/>
+      <c r="A84" s="42"/>
+      <c r="B84" s="43"/>
+      <c r="C84" s="41"/>
+      <c r="D84" s="41"/>
+      <c r="E84" s="87"/>
       <c r="F84" s="39">
         <f t="shared" ref="F84:F117" si="2">D84*E84</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="46"/>
-      <c r="B85" s="47"/>
-      <c r="C85" s="45"/>
-      <c r="D85" s="45"/>
-      <c r="E85" s="48"/>
+      <c r="A85" s="42"/>
+      <c r="B85" s="43"/>
+      <c r="C85" s="41"/>
+      <c r="D85" s="41"/>
+      <c r="E85" s="87"/>
       <c r="F85" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="46"/>
-      <c r="B86" s="47"/>
-      <c r="C86" s="45"/>
-      <c r="D86" s="45"/>
-      <c r="E86" s="48"/>
+      <c r="A86" s="42"/>
+      <c r="B86" s="43"/>
+      <c r="C86" s="41"/>
+      <c r="D86" s="41"/>
+      <c r="E86" s="87"/>
       <c r="F86" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="46"/>
-      <c r="B87" s="47"/>
-      <c r="C87" s="45"/>
-      <c r="D87" s="45"/>
-      <c r="E87" s="48"/>
+      <c r="A87" s="42"/>
+      <c r="B87" s="43"/>
+      <c r="C87" s="41"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="87"/>
       <c r="F87" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="46"/>
-      <c r="B88" s="47"/>
-      <c r="C88" s="45"/>
-      <c r="D88" s="45"/>
-      <c r="E88" s="48"/>
+      <c r="A88" s="42"/>
+      <c r="B88" s="43"/>
+      <c r="C88" s="41"/>
+      <c r="D88" s="41"/>
+      <c r="E88" s="87"/>
       <c r="F88" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="46"/>
-      <c r="B89" s="47"/>
-      <c r="C89" s="45"/>
-      <c r="D89" s="45"/>
-      <c r="E89" s="48"/>
+      <c r="A89" s="42"/>
+      <c r="B89" s="43"/>
+      <c r="C89" s="41"/>
+      <c r="D89" s="41"/>
+      <c r="E89" s="87"/>
       <c r="F89" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="46"/>
-      <c r="B90" s="47"/>
-      <c r="C90" s="45"/>
-      <c r="D90" s="45"/>
-      <c r="E90" s="48"/>
+      <c r="A90" s="42"/>
+      <c r="B90" s="43"/>
+      <c r="C90" s="41"/>
+      <c r="D90" s="41"/>
+      <c r="E90" s="87"/>
       <c r="F90" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="46"/>
-      <c r="B91" s="47"/>
-      <c r="C91" s="45"/>
-      <c r="D91" s="45"/>
-      <c r="E91" s="48"/>
+      <c r="A91" s="42"/>
+      <c r="B91" s="43"/>
+      <c r="C91" s="41"/>
+      <c r="D91" s="41"/>
+      <c r="E91" s="87"/>
       <c r="F91" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="46"/>
-      <c r="B92" s="47"/>
-      <c r="C92" s="45"/>
-      <c r="D92" s="45"/>
-      <c r="E92" s="48"/>
+      <c r="A92" s="42"/>
+      <c r="B92" s="43"/>
+      <c r="C92" s="41"/>
+      <c r="D92" s="41"/>
+      <c r="E92" s="87"/>
       <c r="F92" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="46"/>
-      <c r="B93" s="47"/>
-      <c r="C93" s="45"/>
-      <c r="D93" s="45"/>
-      <c r="E93" s="48"/>
+      <c r="A93" s="42"/>
+      <c r="B93" s="43"/>
+      <c r="C93" s="41"/>
+      <c r="D93" s="41"/>
+      <c r="E93" s="87"/>
       <c r="F93" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="46"/>
-      <c r="B94" s="47"/>
-      <c r="C94" s="45"/>
-      <c r="D94" s="45"/>
-      <c r="E94" s="48"/>
+      <c r="A94" s="42"/>
+      <c r="B94" s="43"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="41"/>
+      <c r="E94" s="87"/>
       <c r="F94" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="46"/>
-      <c r="B95" s="47"/>
-      <c r="C95" s="45"/>
-      <c r="D95" s="45"/>
-      <c r="E95" s="48"/>
+      <c r="A95" s="42"/>
+      <c r="B95" s="43"/>
+      <c r="C95" s="41"/>
+      <c r="D95" s="41"/>
+      <c r="E95" s="87"/>
       <c r="F95" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="46"/>
-      <c r="B96" s="47"/>
-      <c r="C96" s="45"/>
-      <c r="D96" s="45"/>
-      <c r="E96" s="48"/>
+      <c r="A96" s="42"/>
+      <c r="B96" s="43"/>
+      <c r="C96" s="41"/>
+      <c r="D96" s="41"/>
+      <c r="E96" s="87"/>
       <c r="F96" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="46"/>
-      <c r="B97" s="47"/>
-      <c r="C97" s="45"/>
-      <c r="D97" s="45"/>
-      <c r="E97" s="48"/>
+      <c r="A97" s="42"/>
+      <c r="B97" s="43"/>
+      <c r="C97" s="41"/>
+      <c r="D97" s="41"/>
+      <c r="E97" s="87"/>
       <c r="F97" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="46"/>
-      <c r="B98" s="47"/>
-      <c r="C98" s="45"/>
-      <c r="D98" s="45"/>
-      <c r="E98" s="48"/>
+      <c r="A98" s="42"/>
+      <c r="B98" s="43"/>
+      <c r="C98" s="41"/>
+      <c r="D98" s="41"/>
+      <c r="E98" s="87"/>
       <c r="F98" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="46"/>
-      <c r="B99" s="47"/>
-      <c r="C99" s="45"/>
-      <c r="D99" s="45"/>
-      <c r="E99" s="48"/>
+      <c r="A99" s="42"/>
+      <c r="B99" s="43"/>
+      <c r="C99" s="41"/>
+      <c r="D99" s="41"/>
+      <c r="E99" s="87"/>
       <c r="F99" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="46"/>
-      <c r="B100" s="47"/>
-      <c r="C100" s="45"/>
-      <c r="D100" s="45"/>
-      <c r="E100" s="48"/>
+      <c r="A100" s="42"/>
+      <c r="B100" s="43"/>
+      <c r="C100" s="41"/>
+      <c r="D100" s="41"/>
+      <c r="E100" s="87"/>
       <c r="F100" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="46"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="45"/>
-      <c r="D101" s="45"/>
-      <c r="E101" s="48"/>
+      <c r="A101" s="42"/>
+      <c r="B101" s="43"/>
+      <c r="C101" s="41"/>
+      <c r="D101" s="41"/>
+      <c r="E101" s="87"/>
       <c r="F101" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="46"/>
-      <c r="B102" s="47"/>
-      <c r="C102" s="45"/>
-      <c r="D102" s="45"/>
-      <c r="E102" s="48"/>
+      <c r="A102" s="42"/>
+      <c r="B102" s="43"/>
+      <c r="C102" s="41"/>
+      <c r="D102" s="41"/>
+      <c r="E102" s="87"/>
       <c r="F102" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="46"/>
-      <c r="B103" s="47"/>
-      <c r="C103" s="45"/>
-      <c r="D103" s="45"/>
-      <c r="E103" s="48"/>
+      <c r="A103" s="42"/>
+      <c r="B103" s="43"/>
+      <c r="C103" s="41"/>
+      <c r="D103" s="41"/>
+      <c r="E103" s="87"/>
       <c r="F103" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="46"/>
-      <c r="B104" s="47"/>
-      <c r="C104" s="45"/>
-      <c r="D104" s="45"/>
-      <c r="E104" s="48"/>
+      <c r="A104" s="42"/>
+      <c r="B104" s="43"/>
+      <c r="C104" s="41"/>
+      <c r="D104" s="41"/>
+      <c r="E104" s="87"/>
       <c r="F104" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="46"/>
-      <c r="B105" s="47"/>
-      <c r="C105" s="45"/>
-      <c r="D105" s="45"/>
-      <c r="E105" s="48"/>
+      <c r="A105" s="42"/>
+      <c r="B105" s="43"/>
+      <c r="C105" s="41"/>
+      <c r="D105" s="41"/>
+      <c r="E105" s="87"/>
       <c r="F105" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="46"/>
-      <c r="B106" s="47"/>
-      <c r="C106" s="45"/>
-      <c r="D106" s="45"/>
-      <c r="E106" s="48"/>
+      <c r="A106" s="42"/>
+      <c r="B106" s="43"/>
+      <c r="C106" s="41"/>
+      <c r="D106" s="41"/>
+      <c r="E106" s="87"/>
       <c r="F106" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="46"/>
-      <c r="B107" s="47"/>
-      <c r="C107" s="45"/>
-      <c r="D107" s="45"/>
-      <c r="E107" s="48"/>
+      <c r="A107" s="42"/>
+      <c r="B107" s="43"/>
+      <c r="C107" s="41"/>
+      <c r="D107" s="41"/>
+      <c r="E107" s="87"/>
       <c r="F107" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="46"/>
-      <c r="B108" s="47"/>
-      <c r="C108" s="45"/>
-      <c r="D108" s="45"/>
-      <c r="E108" s="48"/>
+      <c r="A108" s="42"/>
+      <c r="B108" s="43"/>
+      <c r="C108" s="41"/>
+      <c r="D108" s="41"/>
+      <c r="E108" s="87"/>
       <c r="F108" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="46"/>
-      <c r="B109" s="47"/>
-      <c r="C109" s="45"/>
-      <c r="D109" s="45"/>
-      <c r="E109" s="48"/>
+      <c r="A109" s="42"/>
+      <c r="B109" s="43"/>
+      <c r="C109" s="41"/>
+      <c r="D109" s="41"/>
+      <c r="E109" s="87"/>
       <c r="F109" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="46"/>
-      <c r="B110" s="47"/>
-      <c r="C110" s="45"/>
-      <c r="D110" s="45"/>
-      <c r="E110" s="48"/>
+      <c r="A110" s="42"/>
+      <c r="B110" s="43"/>
+      <c r="C110" s="41"/>
+      <c r="D110" s="41"/>
+      <c r="E110" s="87"/>
       <c r="F110" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="46"/>
-      <c r="B111" s="47"/>
-      <c r="C111" s="45"/>
-      <c r="D111" s="45"/>
-      <c r="E111" s="48"/>
+      <c r="A111" s="42"/>
+      <c r="B111" s="43"/>
+      <c r="C111" s="41"/>
+      <c r="D111" s="41"/>
+      <c r="E111" s="87"/>
       <c r="F111" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="46"/>
-      <c r="B112" s="47"/>
-      <c r="C112" s="45"/>
-      <c r="D112" s="45"/>
-      <c r="E112" s="48"/>
+      <c r="A112" s="42"/>
+      <c r="B112" s="43"/>
+      <c r="C112" s="41"/>
+      <c r="D112" s="41"/>
+      <c r="E112" s="87"/>
       <c r="F112" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="46"/>
-      <c r="B113" s="47"/>
-      <c r="C113" s="45"/>
-      <c r="D113" s="45"/>
-      <c r="E113" s="48"/>
+      <c r="A113" s="42"/>
+      <c r="B113" s="43"/>
+      <c r="C113" s="41"/>
+      <c r="D113" s="41"/>
+      <c r="E113" s="87"/>
       <c r="F113" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="46"/>
-      <c r="B114" s="47"/>
-      <c r="C114" s="45"/>
-      <c r="D114" s="45"/>
-      <c r="E114" s="48"/>
+      <c r="A114" s="42"/>
+      <c r="B114" s="43"/>
+      <c r="C114" s="41"/>
+      <c r="D114" s="41"/>
+      <c r="E114" s="87"/>
       <c r="F114" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="46"/>
-      <c r="B115" s="47"/>
-      <c r="C115" s="45"/>
-      <c r="D115" s="45"/>
-      <c r="E115" s="48"/>
+      <c r="A115" s="42"/>
+      <c r="B115" s="43"/>
+      <c r="C115" s="41"/>
+      <c r="D115" s="41"/>
+      <c r="E115" s="87"/>
       <c r="F115" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="46"/>
-      <c r="B116" s="47"/>
-      <c r="C116" s="45"/>
-      <c r="D116" s="45"/>
-      <c r="E116" s="48"/>
+      <c r="A116" s="42"/>
+      <c r="B116" s="43"/>
+      <c r="C116" s="41"/>
+      <c r="D116" s="41"/>
+      <c r="E116" s="87"/>
       <c r="F116" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="46"/>
-      <c r="B117" s="47"/>
-      <c r="C117" s="45"/>
-      <c r="D117" s="45"/>
-      <c r="E117" s="48"/>
+      <c r="A117" s="42"/>
+      <c r="B117" s="43"/>
+      <c r="C117" s="41"/>
+      <c r="D117" s="41"/>
+      <c r="E117" s="87"/>
       <c r="F117" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2386,7 +2383,7 @@
       <c r="B118" s="28"/>
       <c r="C118" s="34"/>
       <c r="D118" s="29"/>
-      <c r="E118" s="42"/>
+      <c r="E118" s="88"/>
       <c r="F118" s="39">
         <f t="shared" ref="F118:F143" si="3">D118*E118</f>
         <v>0</v>
@@ -2397,7 +2394,7 @@
       <c r="B119" s="23"/>
       <c r="C119" s="10"/>
       <c r="D119" s="23"/>
-      <c r="E119" s="43"/>
+      <c r="E119" s="89"/>
       <c r="F119" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2408,7 +2405,7 @@
       <c r="B120" s="23"/>
       <c r="C120" s="10"/>
       <c r="D120" s="30"/>
-      <c r="E120" s="43"/>
+      <c r="E120" s="89"/>
       <c r="F120" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2419,12 +2416,12 @@
       <c r="B121" s="23"/>
       <c r="C121" s="10"/>
       <c r="D121" s="30"/>
-      <c r="E121" s="43"/>
+      <c r="E121" s="89"/>
       <c r="F121" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G121" s="91" t="s">
+      <c r="G121" s="44" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2433,12 +2430,12 @@
       <c r="B122" s="23"/>
       <c r="C122" s="10"/>
       <c r="D122" s="30"/>
-      <c r="E122" s="43"/>
+      <c r="E122" s="89"/>
       <c r="F122" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G122" s="91" t="s">
+      <c r="G122" s="44" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2447,7 +2444,7 @@
       <c r="B123" s="23"/>
       <c r="C123" s="10"/>
       <c r="D123" s="30"/>
-      <c r="E123" s="43"/>
+      <c r="E123" s="89"/>
       <c r="F123" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2458,7 +2455,7 @@
       <c r="B124" s="23"/>
       <c r="C124" s="35"/>
       <c r="D124" s="30"/>
-      <c r="E124" s="43"/>
+      <c r="E124" s="89"/>
       <c r="F124" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2469,7 +2466,7 @@
       <c r="B125" s="23"/>
       <c r="C125" s="10"/>
       <c r="D125" s="30"/>
-      <c r="E125" s="43"/>
+      <c r="E125" s="89"/>
       <c r="F125" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2480,7 +2477,7 @@
       <c r="B126" s="23"/>
       <c r="C126" s="10"/>
       <c r="D126" s="30"/>
-      <c r="E126" s="43"/>
+      <c r="E126" s="89"/>
       <c r="F126" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2491,7 +2488,7 @@
       <c r="B127" s="23"/>
       <c r="C127" s="10"/>
       <c r="D127" s="30"/>
-      <c r="E127" s="43"/>
+      <c r="E127" s="89"/>
       <c r="F127" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2502,7 +2499,7 @@
       <c r="B128" s="23"/>
       <c r="C128" s="10"/>
       <c r="D128" s="30"/>
-      <c r="E128" s="40"/>
+      <c r="E128" s="90"/>
       <c r="F128" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2513,7 +2510,7 @@
       <c r="B129" s="32"/>
       <c r="C129" s="31"/>
       <c r="D129" s="32"/>
-      <c r="E129" s="44"/>
+      <c r="E129" s="40"/>
       <c r="F129" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2524,7 +2521,7 @@
       <c r="B130" s="32"/>
       <c r="C130" s="31"/>
       <c r="D130" s="32"/>
-      <c r="E130" s="44"/>
+      <c r="E130" s="40"/>
       <c r="F130" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2535,7 +2532,7 @@
       <c r="B131" s="33"/>
       <c r="C131" s="36"/>
       <c r="D131" s="30"/>
-      <c r="E131" s="41"/>
+      <c r="E131" s="87"/>
       <c r="F131" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2546,7 +2543,7 @@
       <c r="B132" s="25"/>
       <c r="C132" s="10"/>
       <c r="D132" s="30"/>
-      <c r="E132" s="40"/>
+      <c r="E132" s="90"/>
       <c r="F132" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2557,7 +2554,7 @@
       <c r="B133" s="25"/>
       <c r="C133" s="10"/>
       <c r="D133" s="30"/>
-      <c r="E133" s="40"/>
+      <c r="E133" s="90"/>
       <c r="F133" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2568,7 +2565,7 @@
       <c r="B134" s="25"/>
       <c r="C134" s="37"/>
       <c r="D134" s="30"/>
-      <c r="E134" s="40"/>
+      <c r="E134" s="90"/>
       <c r="F134" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2579,7 +2576,7 @@
       <c r="B135" s="25"/>
       <c r="C135" s="10"/>
       <c r="D135" s="30"/>
-      <c r="E135" s="40"/>
+      <c r="E135" s="90"/>
       <c r="F135" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2590,7 +2587,7 @@
       <c r="B136" s="24"/>
       <c r="C136" s="10"/>
       <c r="D136" s="30"/>
-      <c r="E136" s="40"/>
+      <c r="E136" s="90"/>
       <c r="F136" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2601,7 +2598,7 @@
       <c r="B137" s="24"/>
       <c r="C137" s="10"/>
       <c r="D137" s="30"/>
-      <c r="E137" s="40"/>
+      <c r="E137" s="90"/>
       <c r="F137" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2612,7 +2609,7 @@
       <c r="B138" s="24"/>
       <c r="C138" s="10"/>
       <c r="D138" s="30"/>
-      <c r="E138" s="40"/>
+      <c r="E138" s="90"/>
       <c r="F138" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2623,7 +2620,7 @@
       <c r="B139" s="24"/>
       <c r="C139" s="10"/>
       <c r="D139" s="30"/>
-      <c r="E139" s="40"/>
+      <c r="E139" s="90"/>
       <c r="F139" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2634,7 +2631,7 @@
       <c r="B140" s="24"/>
       <c r="C140" s="10"/>
       <c r="D140" s="30"/>
-      <c r="E140" s="40"/>
+      <c r="E140" s="90"/>
       <c r="F140" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2645,7 +2642,7 @@
       <c r="B141" s="11"/>
       <c r="C141" s="37"/>
       <c r="D141" s="30"/>
-      <c r="E141" s="40"/>
+      <c r="E141" s="90"/>
       <c r="F141" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2656,7 +2653,7 @@
       <c r="B142" s="11"/>
       <c r="C142" s="37"/>
       <c r="D142" s="30"/>
-      <c r="E142" s="40"/>
+      <c r="E142" s="90"/>
       <c r="F142" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2667,7 +2664,7 @@
       <c r="B143" s="11"/>
       <c r="C143" s="37"/>
       <c r="D143" s="38"/>
-      <c r="E143" s="40"/>
+      <c r="E143" s="90"/>
       <c r="F143" s="39">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2677,44 +2674,44 @@
       <c r="A144" s="12"/>
       <c r="B144" s="13"/>
       <c r="C144" s="14"/>
-      <c r="D144" s="58" t="s">
+      <c r="D144" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="E144" s="59"/>
+      <c r="E144" s="75"/>
       <c r="F144" s="9">
         <f>SUM(F9:F143)</f>
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="68" t="s">
+      <c r="A145" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="B145" s="69"/>
-      <c r="C145" s="69"/>
-      <c r="D145" s="69"/>
-      <c r="E145" s="69"/>
-      <c r="F145" s="70"/>
+      <c r="B145" s="85"/>
+      <c r="C145" s="85"/>
+      <c r="D145" s="85"/>
+      <c r="E145" s="85"/>
+      <c r="F145" s="86"/>
     </row>
     <row r="146" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A146" s="60"/>
-      <c r="B146" s="61"/>
-      <c r="C146" s="61"/>
-      <c r="D146" s="61"/>
-      <c r="E146" s="61"/>
-      <c r="F146" s="62"/>
+      <c r="A146" s="76"/>
+      <c r="B146" s="77"/>
+      <c r="C146" s="77"/>
+      <c r="D146" s="77"/>
+      <c r="E146" s="77"/>
+      <c r="F146" s="78"/>
     </row>
     <row r="147" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="63" t="s">
+      <c r="A147" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="B147" s="64"/>
-      <c r="C147" s="65"/>
-      <c r="D147" s="66" t="s">
+      <c r="B147" s="80"/>
+      <c r="C147" s="81"/>
+      <c r="D147" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="E147" s="66"/>
-      <c r="F147" s="67"/>
+      <c r="E147" s="82"/>
+      <c r="F147" s="83"/>
     </row>
     <row r="148" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
@@ -2722,9 +2719,9 @@
       </c>
       <c r="B148" s="15"/>
       <c r="C148" s="21"/>
-      <c r="D148" s="49"/>
-      <c r="E148" s="50"/>
-      <c r="F148" s="51"/>
+      <c r="D148" s="67"/>
+      <c r="E148" s="68"/>
+      <c r="F148" s="69"/>
     </row>
     <row r="149" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
@@ -2732,9 +2729,9 @@
       </c>
       <c r="B149" s="15"/>
       <c r="C149" s="16"/>
-      <c r="D149" s="52"/>
-      <c r="E149" s="52"/>
-      <c r="F149" s="53"/>
+      <c r="D149" s="70"/>
+      <c r="E149" s="70"/>
+      <c r="F149" s="71"/>
     </row>
     <row r="150" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="17" t="s">
@@ -2742,12 +2739,12 @@
       </c>
       <c r="B150" s="18"/>
       <c r="C150" s="22"/>
-      <c r="D150" s="54" t="s">
+      <c r="D150" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="E150" s="54"/>
-      <c r="F150" s="55"/>
-      <c r="G150" s="91" t="s">
+      <c r="E150" s="72"/>
+      <c r="F150" s="73"/>
+      <c r="G150" s="44" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2758,7 +2755,7 @@
       <c r="D151" s="19"/>
       <c r="E151" s="19"/>
       <c r="F151" s="20"/>
-      <c r="G151" s="91" t="s">
+      <c r="G151" s="44" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2767,18 +2764,6 @@
     <sortCondition ref="K6:K131"/>
   </sortState>
   <mergeCells count="23">
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:F5"/>
     <mergeCell ref="D148:F148"/>
     <mergeCell ref="D149:F149"/>
     <mergeCell ref="D150:F150"/>
@@ -2790,6 +2775,18 @@
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="A145:B145"/>
     <mergeCell ref="C145:F145"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="1.7716535433070868" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/pr-template 4p.xlsx
+++ b/backend/templates/pr-template 4p.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9253B3F1-3C9D-4413-BC3E-17AB9B9B72A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8C8438-20E8-42C1-830C-D57170D6D199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -430,9 +430,6 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -489,22 +486,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -523,11 +510,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -651,17 +662,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1082,1680 +1084,1680 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="54"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="57"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
+      <c r="A2" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="60"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="58"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="60"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="63"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="62"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="65"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="64"/>
+      <c r="B5" s="67"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="65" t="s">
+      <c r="E5" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="66"/>
+      <c r="F5" s="69"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="47"/>
-      <c r="B6" s="48"/>
+      <c r="A6" s="50"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="46"/>
+      <c r="F6" s="49"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="54" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="50"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="42"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="87"/>
-      <c r="F9" s="39">
+      <c r="A9" s="37"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="34">
         <f t="shared" ref="F9:F72" si="0">D9*E9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="42"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="87"/>
-      <c r="F10" s="39">
+      <c r="A10" s="37"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="42"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="87"/>
-      <c r="F11" s="39">
+      <c r="A11" s="37"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="87"/>
-      <c r="F12" s="39">
+      <c r="A12" s="37"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="42"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="39">
+      <c r="A13" s="37"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="42"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="39">
+      <c r="A14" s="37"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="42"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="87"/>
-      <c r="F15" s="39">
+      <c r="A15" s="37"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="42"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="39">
+      <c r="A16" s="37"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="42"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="87"/>
-      <c r="F17" s="39">
+      <c r="A17" s="37"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="39">
+      <c r="A18" s="37"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="42"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="39">
+      <c r="A19" s="37"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="42"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="39">
+      <c r="A20" s="37"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="42"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="87"/>
-      <c r="F21" s="39">
+      <c r="A21" s="37"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="42"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="87"/>
-      <c r="F22" s="39">
+      <c r="A22" s="37"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="42"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="87"/>
-      <c r="F23" s="39">
+      <c r="A23" s="37"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="42"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="39">
+      <c r="A24" s="37"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="90"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="42"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="39">
+      <c r="A25" s="37"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="42"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="39">
+      <c r="A26" s="37"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="42"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="39">
+      <c r="A27" s="37"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="90"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="42"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="39">
+      <c r="A28" s="37"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="42"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="87"/>
-      <c r="F29" s="39">
+      <c r="A29" s="37"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="42"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="87"/>
-      <c r="F30" s="39">
+      <c r="A30" s="37"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="42"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="87"/>
-      <c r="F31" s="39">
+      <c r="A31" s="37"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="42"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="87"/>
-      <c r="F32" s="39">
+      <c r="A32" s="37"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="90"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="42"/>
-      <c r="B33" s="43"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="87"/>
-      <c r="F33" s="39">
+      <c r="A33" s="37"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="42"/>
-      <c r="B34" s="43"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="87"/>
-      <c r="F34" s="39">
+      <c r="A34" s="37"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="42"/>
-      <c r="B35" s="43"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="87"/>
-      <c r="F35" s="39">
+      <c r="A35" s="37"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="42"/>
-      <c r="B36" s="43"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="87"/>
-      <c r="F36" s="39">
+      <c r="A36" s="37"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="42"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="87"/>
-      <c r="F37" s="39">
+      <c r="A37" s="37"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="42"/>
-      <c r="B38" s="43"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="87"/>
-      <c r="F38" s="39">
+      <c r="A38" s="37"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="90"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="42"/>
-      <c r="B39" s="43"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="87"/>
-      <c r="F39" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="44" t="s">
+      <c r="A39" s="37"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="38" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="42"/>
-      <c r="B40" s="43"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="44" t="s">
+      <c r="A40" s="37"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="38" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="42"/>
-      <c r="B41" s="43"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="39">
+      <c r="A41" s="37"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="42"/>
-      <c r="B42" s="43"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="87"/>
-      <c r="F42" s="39">
+      <c r="A42" s="37"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="42"/>
-      <c r="B43" s="43"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="87"/>
-      <c r="F43" s="39">
+      <c r="A43" s="37"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="90"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="42"/>
-      <c r="B44" s="43"/>
-      <c r="C44" s="41"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="87"/>
-      <c r="F44" s="39">
+      <c r="A44" s="37"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="90"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="42"/>
-      <c r="B45" s="43"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="87"/>
-      <c r="F45" s="39">
+      <c r="A45" s="37"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="90"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="42"/>
-      <c r="B46" s="43"/>
-      <c r="C46" s="41"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="87"/>
-      <c r="F46" s="39">
+      <c r="A46" s="37"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="90"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="42"/>
-      <c r="B47" s="43"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="87"/>
-      <c r="F47" s="39">
+      <c r="A47" s="37"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="36"/>
+      <c r="E47" s="39"/>
+      <c r="F47" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="42"/>
-      <c r="B48" s="43"/>
-      <c r="C48" s="41"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="87"/>
-      <c r="F48" s="39">
+      <c r="A48" s="37"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="90"/>
+      <c r="D48" s="36"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="42"/>
-      <c r="B49" s="43"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="87"/>
-      <c r="F49" s="39">
+      <c r="A49" s="37"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="90"/>
+      <c r="D49" s="36"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="42"/>
-      <c r="B50" s="43"/>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="87"/>
-      <c r="F50" s="39">
+      <c r="A50" s="37"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="90"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="42"/>
-      <c r="B51" s="43"/>
-      <c r="C51" s="41"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="87"/>
-      <c r="F51" s="39">
+      <c r="A51" s="37"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="90"/>
+      <c r="D51" s="36"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="42"/>
-      <c r="B52" s="43"/>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="87"/>
-      <c r="F52" s="39">
+      <c r="A52" s="37"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="90"/>
+      <c r="D52" s="36"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="42"/>
-      <c r="B53" s="43"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="87"/>
-      <c r="F53" s="39">
+      <c r="A53" s="37"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="90"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="42"/>
-      <c r="B54" s="43"/>
-      <c r="C54" s="41"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="87"/>
-      <c r="F54" s="39">
+      <c r="A54" s="37"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="90"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="42"/>
-      <c r="B55" s="43"/>
-      <c r="C55" s="41"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="87"/>
-      <c r="F55" s="39">
+      <c r="A55" s="37"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="90"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="39"/>
+      <c r="F55" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="42"/>
-      <c r="B56" s="43"/>
-      <c r="C56" s="41"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="87"/>
-      <c r="F56" s="39">
+      <c r="A56" s="37"/>
+      <c r="B56" s="27"/>
+      <c r="C56" s="90"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="42"/>
-      <c r="B57" s="43"/>
-      <c r="C57" s="41"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="87"/>
-      <c r="F57" s="39">
+      <c r="A57" s="37"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="90"/>
+      <c r="D57" s="36"/>
+      <c r="E57" s="39"/>
+      <c r="F57" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="42"/>
-      <c r="B58" s="43"/>
-      <c r="C58" s="41"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="87"/>
-      <c r="F58" s="39">
+      <c r="A58" s="37"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="90"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="39"/>
+      <c r="F58" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="42"/>
-      <c r="B59" s="43"/>
-      <c r="C59" s="41"/>
-      <c r="D59" s="41"/>
-      <c r="E59" s="87"/>
-      <c r="F59" s="39">
+      <c r="A59" s="37"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="90"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="42"/>
-      <c r="B60" s="43"/>
-      <c r="C60" s="41"/>
-      <c r="D60" s="41"/>
-      <c r="E60" s="87"/>
-      <c r="F60" s="39">
+      <c r="A60" s="37"/>
+      <c r="B60" s="27"/>
+      <c r="C60" s="90"/>
+      <c r="D60" s="36"/>
+      <c r="E60" s="39"/>
+      <c r="F60" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="42"/>
-      <c r="B61" s="43"/>
-      <c r="C61" s="41"/>
-      <c r="D61" s="41"/>
-      <c r="E61" s="87"/>
-      <c r="F61" s="39">
+      <c r="A61" s="37"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="90"/>
+      <c r="D61" s="36"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="42"/>
-      <c r="B62" s="43"/>
-      <c r="C62" s="41"/>
-      <c r="D62" s="41"/>
-      <c r="E62" s="87"/>
-      <c r="F62" s="39">
+      <c r="A62" s="37"/>
+      <c r="B62" s="27"/>
+      <c r="C62" s="90"/>
+      <c r="D62" s="36"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="42"/>
-      <c r="B63" s="43"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="87"/>
-      <c r="F63" s="39">
+      <c r="A63" s="37"/>
+      <c r="B63" s="27"/>
+      <c r="C63" s="90"/>
+      <c r="D63" s="36"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="42"/>
-      <c r="B64" s="43"/>
-      <c r="C64" s="41"/>
-      <c r="D64" s="41"/>
-      <c r="E64" s="87"/>
-      <c r="F64" s="39">
+      <c r="A64" s="37"/>
+      <c r="B64" s="27"/>
+      <c r="C64" s="90"/>
+      <c r="D64" s="36"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="42"/>
-      <c r="B65" s="43"/>
-      <c r="C65" s="41"/>
-      <c r="D65" s="41"/>
-      <c r="E65" s="87"/>
-      <c r="F65" s="39">
+      <c r="A65" s="37"/>
+      <c r="B65" s="27"/>
+      <c r="C65" s="90"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="42"/>
-      <c r="B66" s="43"/>
-      <c r="C66" s="41"/>
-      <c r="D66" s="41"/>
-      <c r="E66" s="87"/>
-      <c r="F66" s="39">
+      <c r="A66" s="37"/>
+      <c r="B66" s="27"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="42"/>
-      <c r="B67" s="43"/>
-      <c r="C67" s="41"/>
-      <c r="D67" s="41"/>
-      <c r="E67" s="87"/>
-      <c r="F67" s="39">
+      <c r="A67" s="37"/>
+      <c r="B67" s="27"/>
+      <c r="C67" s="90"/>
+      <c r="D67" s="36"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="42"/>
-      <c r="B68" s="43"/>
-      <c r="C68" s="41"/>
-      <c r="D68" s="41"/>
-      <c r="E68" s="87"/>
-      <c r="F68" s="39">
+      <c r="A68" s="37"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="90"/>
+      <c r="D68" s="36"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="42"/>
-      <c r="B69" s="43"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="87"/>
-      <c r="F69" s="39">
+      <c r="A69" s="37"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="90"/>
+      <c r="D69" s="36"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="42"/>
-      <c r="B70" s="43"/>
-      <c r="C70" s="41"/>
-      <c r="D70" s="41"/>
-      <c r="E70" s="87"/>
-      <c r="F70" s="39">
+      <c r="A70" s="37"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="90"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="42"/>
-      <c r="B71" s="43"/>
-      <c r="C71" s="41"/>
-      <c r="D71" s="41"/>
-      <c r="E71" s="87"/>
-      <c r="F71" s="39">
+      <c r="A71" s="37"/>
+      <c r="B71" s="27"/>
+      <c r="C71" s="90"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="42"/>
-      <c r="B72" s="43"/>
-      <c r="C72" s="41"/>
-      <c r="D72" s="41"/>
-      <c r="E72" s="87"/>
-      <c r="F72" s="39">
+      <c r="A72" s="37"/>
+      <c r="B72" s="27"/>
+      <c r="C72" s="90"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="42"/>
-      <c r="B73" s="43"/>
-      <c r="C73" s="41"/>
-      <c r="D73" s="41"/>
-      <c r="E73" s="87"/>
-      <c r="F73" s="39">
+      <c r="A73" s="37"/>
+      <c r="B73" s="27"/>
+      <c r="C73" s="90"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="34">
         <f t="shared" ref="F73:F83" si="1">D73*E73</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="42"/>
-      <c r="B74" s="43"/>
-      <c r="C74" s="41"/>
-      <c r="D74" s="41"/>
-      <c r="E74" s="87"/>
-      <c r="F74" s="39">
+      <c r="A74" s="37"/>
+      <c r="B74" s="27"/>
+      <c r="C74" s="90"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="42"/>
-      <c r="B75" s="43"/>
-      <c r="C75" s="41"/>
-      <c r="D75" s="41"/>
-      <c r="E75" s="87"/>
-      <c r="F75" s="39">
+      <c r="A75" s="37"/>
+      <c r="B75" s="27"/>
+      <c r="C75" s="90"/>
+      <c r="D75" s="36"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="42"/>
-      <c r="B76" s="43"/>
-      <c r="C76" s="41"/>
-      <c r="D76" s="41"/>
-      <c r="E76" s="87"/>
-      <c r="F76" s="39">
+      <c r="A76" s="37"/>
+      <c r="B76" s="27"/>
+      <c r="C76" s="90"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="42"/>
-      <c r="B77" s="43"/>
-      <c r="C77" s="41"/>
-      <c r="D77" s="41"/>
-      <c r="E77" s="87"/>
-      <c r="F77" s="39">
+      <c r="A77" s="37"/>
+      <c r="B77" s="27"/>
+      <c r="C77" s="90"/>
+      <c r="D77" s="36"/>
+      <c r="E77" s="39"/>
+      <c r="F77" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="42"/>
-      <c r="B78" s="43"/>
-      <c r="C78" s="41"/>
-      <c r="D78" s="41"/>
-      <c r="E78" s="87"/>
-      <c r="F78" s="39">
+      <c r="A78" s="37"/>
+      <c r="B78" s="27"/>
+      <c r="C78" s="90"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="39"/>
+      <c r="F78" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="42"/>
-      <c r="B79" s="43"/>
-      <c r="C79" s="41"/>
-      <c r="D79" s="41"/>
-      <c r="E79" s="87"/>
-      <c r="F79" s="39">
+      <c r="A79" s="37"/>
+      <c r="B79" s="27"/>
+      <c r="C79" s="90"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="39"/>
+      <c r="F79" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="42"/>
-      <c r="B80" s="43"/>
-      <c r="C80" s="41"/>
-      <c r="D80" s="41"/>
-      <c r="E80" s="87"/>
-      <c r="F80" s="39">
+      <c r="A80" s="37"/>
+      <c r="B80" s="27"/>
+      <c r="C80" s="90"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="39"/>
+      <c r="F80" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G80" s="44" t="s">
+      <c r="G80" s="38" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="42"/>
-      <c r="B81" s="43"/>
-      <c r="C81" s="41"/>
-      <c r="D81" s="41"/>
-      <c r="E81" s="87"/>
-      <c r="F81" s="39">
+      <c r="A81" s="37"/>
+      <c r="B81" s="27"/>
+      <c r="C81" s="90"/>
+      <c r="D81" s="36"/>
+      <c r="E81" s="39"/>
+      <c r="F81" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G81" s="44" t="s">
+      <c r="G81" s="38" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="42"/>
-      <c r="B82" s="43"/>
-      <c r="C82" s="41"/>
-      <c r="D82" s="41"/>
-      <c r="E82" s="87"/>
-      <c r="F82" s="39">
+      <c r="A82" s="37"/>
+      <c r="B82" s="27"/>
+      <c r="C82" s="90"/>
+      <c r="D82" s="36"/>
+      <c r="E82" s="39"/>
+      <c r="F82" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="42"/>
-      <c r="B83" s="43"/>
-      <c r="C83" s="41"/>
-      <c r="D83" s="41"/>
-      <c r="E83" s="87"/>
-      <c r="F83" s="39">
+      <c r="A83" s="37"/>
+      <c r="B83" s="27"/>
+      <c r="C83" s="90"/>
+      <c r="D83" s="36"/>
+      <c r="E83" s="39"/>
+      <c r="F83" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="42"/>
-      <c r="B84" s="43"/>
-      <c r="C84" s="41"/>
-      <c r="D84" s="41"/>
-      <c r="E84" s="87"/>
-      <c r="F84" s="39">
+      <c r="A84" s="37"/>
+      <c r="B84" s="27"/>
+      <c r="C84" s="90"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="39"/>
+      <c r="F84" s="34">
         <f t="shared" ref="F84:F117" si="2">D84*E84</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="42"/>
-      <c r="B85" s="43"/>
-      <c r="C85" s="41"/>
-      <c r="D85" s="41"/>
-      <c r="E85" s="87"/>
-      <c r="F85" s="39">
+      <c r="A85" s="37"/>
+      <c r="B85" s="27"/>
+      <c r="C85" s="90"/>
+      <c r="D85" s="36"/>
+      <c r="E85" s="39"/>
+      <c r="F85" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="42"/>
-      <c r="B86" s="43"/>
-      <c r="C86" s="41"/>
-      <c r="D86" s="41"/>
-      <c r="E86" s="87"/>
-      <c r="F86" s="39">
+      <c r="A86" s="37"/>
+      <c r="B86" s="27"/>
+      <c r="C86" s="90"/>
+      <c r="D86" s="36"/>
+      <c r="E86" s="39"/>
+      <c r="F86" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="42"/>
-      <c r="B87" s="43"/>
-      <c r="C87" s="41"/>
-      <c r="D87" s="41"/>
-      <c r="E87" s="87"/>
-      <c r="F87" s="39">
+      <c r="A87" s="37"/>
+      <c r="B87" s="27"/>
+      <c r="C87" s="90"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="42"/>
-      <c r="B88" s="43"/>
-      <c r="C88" s="41"/>
-      <c r="D88" s="41"/>
-      <c r="E88" s="87"/>
-      <c r="F88" s="39">
+      <c r="A88" s="37"/>
+      <c r="B88" s="27"/>
+      <c r="C88" s="90"/>
+      <c r="D88" s="36"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="42"/>
-      <c r="B89" s="43"/>
-      <c r="C89" s="41"/>
-      <c r="D89" s="41"/>
-      <c r="E89" s="87"/>
-      <c r="F89" s="39">
+      <c r="A89" s="37"/>
+      <c r="B89" s="27"/>
+      <c r="C89" s="90"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="39"/>
+      <c r="F89" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="42"/>
-      <c r="B90" s="43"/>
-      <c r="C90" s="41"/>
-      <c r="D90" s="41"/>
-      <c r="E90" s="87"/>
-      <c r="F90" s="39">
+      <c r="A90" s="37"/>
+      <c r="B90" s="27"/>
+      <c r="C90" s="90"/>
+      <c r="D90" s="36"/>
+      <c r="E90" s="39"/>
+      <c r="F90" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="42"/>
-      <c r="B91" s="43"/>
-      <c r="C91" s="41"/>
-      <c r="D91" s="41"/>
-      <c r="E91" s="87"/>
-      <c r="F91" s="39">
+      <c r="A91" s="37"/>
+      <c r="B91" s="27"/>
+      <c r="C91" s="90"/>
+      <c r="D91" s="36"/>
+      <c r="E91" s="39"/>
+      <c r="F91" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="42"/>
-      <c r="B92" s="43"/>
-      <c r="C92" s="41"/>
-      <c r="D92" s="41"/>
-      <c r="E92" s="87"/>
-      <c r="F92" s="39">
+      <c r="A92" s="37"/>
+      <c r="B92" s="27"/>
+      <c r="C92" s="90"/>
+      <c r="D92" s="36"/>
+      <c r="E92" s="39"/>
+      <c r="F92" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="42"/>
-      <c r="B93" s="43"/>
-      <c r="C93" s="41"/>
-      <c r="D93" s="41"/>
-      <c r="E93" s="87"/>
-      <c r="F93" s="39">
+      <c r="A93" s="37"/>
+      <c r="B93" s="27"/>
+      <c r="C93" s="90"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="39"/>
+      <c r="F93" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="42"/>
-      <c r="B94" s="43"/>
-      <c r="C94" s="41"/>
-      <c r="D94" s="41"/>
-      <c r="E94" s="87"/>
-      <c r="F94" s="39">
+      <c r="A94" s="37"/>
+      <c r="B94" s="27"/>
+      <c r="C94" s="90"/>
+      <c r="D94" s="36"/>
+      <c r="E94" s="39"/>
+      <c r="F94" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="42"/>
-      <c r="B95" s="43"/>
-      <c r="C95" s="41"/>
-      <c r="D95" s="41"/>
-      <c r="E95" s="87"/>
-      <c r="F95" s="39">
+      <c r="A95" s="37"/>
+      <c r="B95" s="27"/>
+      <c r="C95" s="90"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="39"/>
+      <c r="F95" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="42"/>
-      <c r="B96" s="43"/>
-      <c r="C96" s="41"/>
-      <c r="D96" s="41"/>
-      <c r="E96" s="87"/>
-      <c r="F96" s="39">
+      <c r="A96" s="37"/>
+      <c r="B96" s="27"/>
+      <c r="C96" s="90"/>
+      <c r="D96" s="36"/>
+      <c r="E96" s="39"/>
+      <c r="F96" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="42"/>
-      <c r="B97" s="43"/>
-      <c r="C97" s="41"/>
-      <c r="D97" s="41"/>
-      <c r="E97" s="87"/>
-      <c r="F97" s="39">
+      <c r="A97" s="37"/>
+      <c r="B97" s="27"/>
+      <c r="C97" s="90"/>
+      <c r="D97" s="36"/>
+      <c r="E97" s="39"/>
+      <c r="F97" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="42"/>
-      <c r="B98" s="43"/>
-      <c r="C98" s="41"/>
-      <c r="D98" s="41"/>
-      <c r="E98" s="87"/>
-      <c r="F98" s="39">
+      <c r="A98" s="37"/>
+      <c r="B98" s="27"/>
+      <c r="C98" s="90"/>
+      <c r="D98" s="36"/>
+      <c r="E98" s="39"/>
+      <c r="F98" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="42"/>
-      <c r="B99" s="43"/>
-      <c r="C99" s="41"/>
-      <c r="D99" s="41"/>
-      <c r="E99" s="87"/>
-      <c r="F99" s="39">
+      <c r="A99" s="37"/>
+      <c r="B99" s="27"/>
+      <c r="C99" s="90"/>
+      <c r="D99" s="36"/>
+      <c r="E99" s="39"/>
+      <c r="F99" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="42"/>
-      <c r="B100" s="43"/>
-      <c r="C100" s="41"/>
-      <c r="D100" s="41"/>
-      <c r="E100" s="87"/>
-      <c r="F100" s="39">
+      <c r="A100" s="37"/>
+      <c r="B100" s="27"/>
+      <c r="C100" s="90"/>
+      <c r="D100" s="36"/>
+      <c r="E100" s="39"/>
+      <c r="F100" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="42"/>
-      <c r="B101" s="43"/>
-      <c r="C101" s="41"/>
-      <c r="D101" s="41"/>
-      <c r="E101" s="87"/>
-      <c r="F101" s="39">
+      <c r="A101" s="37"/>
+      <c r="B101" s="27"/>
+      <c r="C101" s="90"/>
+      <c r="D101" s="36"/>
+      <c r="E101" s="39"/>
+      <c r="F101" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="42"/>
-      <c r="B102" s="43"/>
-      <c r="C102" s="41"/>
-      <c r="D102" s="41"/>
-      <c r="E102" s="87"/>
-      <c r="F102" s="39">
+      <c r="A102" s="37"/>
+      <c r="B102" s="27"/>
+      <c r="C102" s="90"/>
+      <c r="D102" s="36"/>
+      <c r="E102" s="39"/>
+      <c r="F102" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="42"/>
-      <c r="B103" s="43"/>
-      <c r="C103" s="41"/>
-      <c r="D103" s="41"/>
-      <c r="E103" s="87"/>
-      <c r="F103" s="39">
+      <c r="A103" s="37"/>
+      <c r="B103" s="27"/>
+      <c r="C103" s="90"/>
+      <c r="D103" s="36"/>
+      <c r="E103" s="39"/>
+      <c r="F103" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="42"/>
-      <c r="B104" s="43"/>
-      <c r="C104" s="41"/>
-      <c r="D104" s="41"/>
-      <c r="E104" s="87"/>
-      <c r="F104" s="39">
+      <c r="A104" s="37"/>
+      <c r="B104" s="27"/>
+      <c r="C104" s="90"/>
+      <c r="D104" s="36"/>
+      <c r="E104" s="39"/>
+      <c r="F104" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="42"/>
-      <c r="B105" s="43"/>
-      <c r="C105" s="41"/>
-      <c r="D105" s="41"/>
-      <c r="E105" s="87"/>
-      <c r="F105" s="39">
+      <c r="A105" s="37"/>
+      <c r="B105" s="27"/>
+      <c r="C105" s="90"/>
+      <c r="D105" s="36"/>
+      <c r="E105" s="39"/>
+      <c r="F105" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="42"/>
-      <c r="B106" s="43"/>
-      <c r="C106" s="41"/>
-      <c r="D106" s="41"/>
-      <c r="E106" s="87"/>
-      <c r="F106" s="39">
+      <c r="A106" s="37"/>
+      <c r="B106" s="27"/>
+      <c r="C106" s="90"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="39"/>
+      <c r="F106" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="42"/>
-      <c r="B107" s="43"/>
-      <c r="C107" s="41"/>
-      <c r="D107" s="41"/>
-      <c r="E107" s="87"/>
-      <c r="F107" s="39">
+      <c r="A107" s="37"/>
+      <c r="B107" s="27"/>
+      <c r="C107" s="90"/>
+      <c r="D107" s="36"/>
+      <c r="E107" s="39"/>
+      <c r="F107" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="42"/>
-      <c r="B108" s="43"/>
-      <c r="C108" s="41"/>
-      <c r="D108" s="41"/>
-      <c r="E108" s="87"/>
-      <c r="F108" s="39">
+      <c r="A108" s="37"/>
+      <c r="B108" s="27"/>
+      <c r="C108" s="90"/>
+      <c r="D108" s="36"/>
+      <c r="E108" s="39"/>
+      <c r="F108" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="42"/>
-      <c r="B109" s="43"/>
-      <c r="C109" s="41"/>
-      <c r="D109" s="41"/>
-      <c r="E109" s="87"/>
-      <c r="F109" s="39">
+      <c r="A109" s="37"/>
+      <c r="B109" s="27"/>
+      <c r="C109" s="90"/>
+      <c r="D109" s="36"/>
+      <c r="E109" s="39"/>
+      <c r="F109" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="42"/>
-      <c r="B110" s="43"/>
-      <c r="C110" s="41"/>
-      <c r="D110" s="41"/>
-      <c r="E110" s="87"/>
-      <c r="F110" s="39">
+      <c r="A110" s="37"/>
+      <c r="B110" s="27"/>
+      <c r="C110" s="90"/>
+      <c r="D110" s="36"/>
+      <c r="E110" s="39"/>
+      <c r="F110" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="42"/>
-      <c r="B111" s="43"/>
-      <c r="C111" s="41"/>
-      <c r="D111" s="41"/>
-      <c r="E111" s="87"/>
-      <c r="F111" s="39">
+      <c r="A111" s="37"/>
+      <c r="B111" s="27"/>
+      <c r="C111" s="90"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="39"/>
+      <c r="F111" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="42"/>
-      <c r="B112" s="43"/>
-      <c r="C112" s="41"/>
-      <c r="D112" s="41"/>
-      <c r="E112" s="87"/>
-      <c r="F112" s="39">
+      <c r="A112" s="37"/>
+      <c r="B112" s="27"/>
+      <c r="C112" s="90"/>
+      <c r="D112" s="36"/>
+      <c r="E112" s="39"/>
+      <c r="F112" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="42"/>
-      <c r="B113" s="43"/>
-      <c r="C113" s="41"/>
-      <c r="D113" s="41"/>
-      <c r="E113" s="87"/>
-      <c r="F113" s="39">
+      <c r="A113" s="37"/>
+      <c r="B113" s="27"/>
+      <c r="C113" s="90"/>
+      <c r="D113" s="36"/>
+      <c r="E113" s="39"/>
+      <c r="F113" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="42"/>
-      <c r="B114" s="43"/>
-      <c r="C114" s="41"/>
-      <c r="D114" s="41"/>
-      <c r="E114" s="87"/>
-      <c r="F114" s="39">
+      <c r="A114" s="37"/>
+      <c r="B114" s="27"/>
+      <c r="C114" s="90"/>
+      <c r="D114" s="36"/>
+      <c r="E114" s="39"/>
+      <c r="F114" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="42"/>
-      <c r="B115" s="43"/>
-      <c r="C115" s="41"/>
-      <c r="D115" s="41"/>
-      <c r="E115" s="87"/>
-      <c r="F115" s="39">
+      <c r="A115" s="37"/>
+      <c r="B115" s="27"/>
+      <c r="C115" s="90"/>
+      <c r="D115" s="36"/>
+      <c r="E115" s="39"/>
+      <c r="F115" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="42"/>
-      <c r="B116" s="43"/>
-      <c r="C116" s="41"/>
-      <c r="D116" s="41"/>
-      <c r="E116" s="87"/>
-      <c r="F116" s="39">
+      <c r="A116" s="37"/>
+      <c r="B116" s="27"/>
+      <c r="C116" s="90"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="39"/>
+      <c r="F116" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="42"/>
-      <c r="B117" s="43"/>
-      <c r="C117" s="41"/>
-      <c r="D117" s="41"/>
-      <c r="E117" s="87"/>
-      <c r="F117" s="39">
+      <c r="A117" s="37"/>
+      <c r="B117" s="27"/>
+      <c r="C117" s="90"/>
+      <c r="D117" s="36"/>
+      <c r="E117" s="39"/>
+      <c r="F117" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="8"/>
-      <c r="B118" s="28"/>
-      <c r="C118" s="34"/>
-      <c r="D118" s="29"/>
-      <c r="E118" s="88"/>
-      <c r="F118" s="39">
+      <c r="B118" s="27"/>
+      <c r="C118" s="43"/>
+      <c r="D118" s="28"/>
+      <c r="E118" s="40"/>
+      <c r="F118" s="34">
         <f t="shared" ref="F118:F143" si="3">D118*E118</f>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="8"/>
-      <c r="B119" s="23"/>
-      <c r="C119" s="10"/>
-      <c r="D119" s="23"/>
-      <c r="E119" s="89"/>
-      <c r="F119" s="39">
+      <c r="B119" s="22"/>
+      <c r="C119" s="44"/>
+      <c r="D119" s="22"/>
+      <c r="E119" s="41"/>
+      <c r="F119" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="8"/>
-      <c r="B120" s="23"/>
-      <c r="C120" s="10"/>
-      <c r="D120" s="30"/>
-      <c r="E120" s="89"/>
-      <c r="F120" s="39">
+      <c r="B120" s="22"/>
+      <c r="C120" s="44"/>
+      <c r="D120" s="29"/>
+      <c r="E120" s="41"/>
+      <c r="F120" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="8"/>
-      <c r="B121" s="23"/>
-      <c r="C121" s="10"/>
-      <c r="D121" s="30"/>
-      <c r="E121" s="89"/>
-      <c r="F121" s="39">
+      <c r="B121" s="22"/>
+      <c r="C121" s="44"/>
+      <c r="D121" s="29"/>
+      <c r="E121" s="41"/>
+      <c r="F121" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G121" s="44" t="s">
+      <c r="G121" s="38" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="8"/>
-      <c r="B122" s="23"/>
-      <c r="C122" s="10"/>
-      <c r="D122" s="30"/>
-      <c r="E122" s="89"/>
-      <c r="F122" s="39">
+      <c r="B122" s="22"/>
+      <c r="C122" s="44"/>
+      <c r="D122" s="29"/>
+      <c r="E122" s="41"/>
+      <c r="F122" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G122" s="44" t="s">
+      <c r="G122" s="38" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="8"/>
-      <c r="B123" s="23"/>
-      <c r="C123" s="10"/>
-      <c r="D123" s="30"/>
-      <c r="E123" s="89"/>
-      <c r="F123" s="39">
+      <c r="B123" s="22"/>
+      <c r="C123" s="44"/>
+      <c r="D123" s="29"/>
+      <c r="E123" s="41"/>
+      <c r="F123" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="8"/>
-      <c r="B124" s="23"/>
-      <c r="C124" s="35"/>
-      <c r="D124" s="30"/>
-      <c r="E124" s="89"/>
-      <c r="F124" s="39">
+      <c r="B124" s="22"/>
+      <c r="C124" s="45"/>
+      <c r="D124" s="29"/>
+      <c r="E124" s="41"/>
+      <c r="F124" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="8"/>
-      <c r="B125" s="23"/>
-      <c r="C125" s="10"/>
-      <c r="D125" s="30"/>
-      <c r="E125" s="89"/>
-      <c r="F125" s="39">
+      <c r="B125" s="22"/>
+      <c r="C125" s="44"/>
+      <c r="D125" s="29"/>
+      <c r="E125" s="41"/>
+      <c r="F125" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="8"/>
-      <c r="B126" s="23"/>
-      <c r="C126" s="10"/>
-      <c r="D126" s="30"/>
-      <c r="E126" s="89"/>
-      <c r="F126" s="39">
+      <c r="B126" s="22"/>
+      <c r="C126" s="44"/>
+      <c r="D126" s="29"/>
+      <c r="E126" s="41"/>
+      <c r="F126" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="8"/>
-      <c r="B127" s="23"/>
-      <c r="C127" s="10"/>
-      <c r="D127" s="30"/>
-      <c r="E127" s="89"/>
-      <c r="F127" s="39">
+      <c r="B127" s="22"/>
+      <c r="C127" s="44"/>
+      <c r="D127" s="29"/>
+      <c r="E127" s="41"/>
+      <c r="F127" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="8"/>
-      <c r="B128" s="23"/>
-      <c r="C128" s="10"/>
-      <c r="D128" s="30"/>
-      <c r="E128" s="90"/>
-      <c r="F128" s="39">
+      <c r="B128" s="22"/>
+      <c r="C128" s="44"/>
+      <c r="D128" s="29"/>
+      <c r="E128" s="42"/>
+      <c r="F128" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="8"/>
-      <c r="B129" s="32"/>
-      <c r="C129" s="31"/>
-      <c r="D129" s="32"/>
-      <c r="E129" s="40"/>
-      <c r="F129" s="39">
+      <c r="B129" s="30"/>
+      <c r="C129" s="46"/>
+      <c r="D129" s="30"/>
+      <c r="E129" s="35"/>
+      <c r="F129" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="8"/>
-      <c r="B130" s="32"/>
-      <c r="C130" s="31"/>
-      <c r="D130" s="32"/>
-      <c r="E130" s="40"/>
-      <c r="F130" s="39">
+      <c r="B130" s="30"/>
+      <c r="C130" s="46"/>
+      <c r="D130" s="30"/>
+      <c r="E130" s="35"/>
+      <c r="F130" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="8"/>
-      <c r="B131" s="33"/>
-      <c r="C131" s="36"/>
-      <c r="D131" s="30"/>
-      <c r="E131" s="87"/>
-      <c r="F131" s="39">
+      <c r="B131" s="31"/>
+      <c r="C131" s="47"/>
+      <c r="D131" s="29"/>
+      <c r="E131" s="39"/>
+      <c r="F131" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="8"/>
-      <c r="B132" s="25"/>
-      <c r="C132" s="10"/>
-      <c r="D132" s="30"/>
-      <c r="E132" s="90"/>
-      <c r="F132" s="39">
+      <c r="B132" s="24"/>
+      <c r="C132" s="44"/>
+      <c r="D132" s="29"/>
+      <c r="E132" s="42"/>
+      <c r="F132" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="8"/>
-      <c r="B133" s="25"/>
-      <c r="C133" s="10"/>
-      <c r="D133" s="30"/>
-      <c r="E133" s="90"/>
-      <c r="F133" s="39">
+      <c r="B133" s="24"/>
+      <c r="C133" s="44"/>
+      <c r="D133" s="29"/>
+      <c r="E133" s="42"/>
+      <c r="F133" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="8"/>
-      <c r="B134" s="25"/>
-      <c r="C134" s="37"/>
-      <c r="D134" s="30"/>
-      <c r="E134" s="90"/>
-      <c r="F134" s="39">
+      <c r="B134" s="24"/>
+      <c r="C134" s="32"/>
+      <c r="D134" s="29"/>
+      <c r="E134" s="42"/>
+      <c r="F134" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="8"/>
-      <c r="B135" s="25"/>
-      <c r="C135" s="10"/>
-      <c r="D135" s="30"/>
-      <c r="E135" s="90"/>
-      <c r="F135" s="39">
+      <c r="B135" s="24"/>
+      <c r="C135" s="44"/>
+      <c r="D135" s="29"/>
+      <c r="E135" s="42"/>
+      <c r="F135" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="8"/>
-      <c r="B136" s="24"/>
-      <c r="C136" s="10"/>
-      <c r="D136" s="30"/>
-      <c r="E136" s="90"/>
-      <c r="F136" s="39">
+      <c r="B136" s="23"/>
+      <c r="C136" s="44"/>
+      <c r="D136" s="29"/>
+      <c r="E136" s="42"/>
+      <c r="F136" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="8"/>
-      <c r="B137" s="24"/>
-      <c r="C137" s="10"/>
-      <c r="D137" s="30"/>
-      <c r="E137" s="90"/>
-      <c r="F137" s="39">
+      <c r="B137" s="23"/>
+      <c r="C137" s="44"/>
+      <c r="D137" s="29"/>
+      <c r="E137" s="42"/>
+      <c r="F137" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="8"/>
-      <c r="B138" s="24"/>
-      <c r="C138" s="10"/>
-      <c r="D138" s="30"/>
-      <c r="E138" s="90"/>
-      <c r="F138" s="39">
+      <c r="B138" s="23"/>
+      <c r="C138" s="44"/>
+      <c r="D138" s="29"/>
+      <c r="E138" s="42"/>
+      <c r="F138" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="8"/>
-      <c r="B139" s="24"/>
-      <c r="C139" s="10"/>
-      <c r="D139" s="30"/>
-      <c r="E139" s="90"/>
-      <c r="F139" s="39">
+      <c r="B139" s="23"/>
+      <c r="C139" s="44"/>
+      <c r="D139" s="29"/>
+      <c r="E139" s="42"/>
+      <c r="F139" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="8"/>
-      <c r="B140" s="24"/>
-      <c r="C140" s="10"/>
-      <c r="D140" s="30"/>
-      <c r="E140" s="90"/>
-      <c r="F140" s="39">
+      <c r="B140" s="23"/>
+      <c r="C140" s="44"/>
+      <c r="D140" s="29"/>
+      <c r="E140" s="42"/>
+      <c r="F140" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="8"/>
-      <c r="B141" s="11"/>
-      <c r="C141" s="37"/>
-      <c r="D141" s="30"/>
-      <c r="E141" s="90"/>
-      <c r="F141" s="39">
+      <c r="B141" s="10"/>
+      <c r="C141" s="32"/>
+      <c r="D141" s="29"/>
+      <c r="E141" s="42"/>
+      <c r="F141" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="8"/>
-      <c r="B142" s="11"/>
-      <c r="C142" s="37"/>
-      <c r="D142" s="30"/>
-      <c r="E142" s="90"/>
-      <c r="F142" s="39">
+      <c r="B142" s="10"/>
+      <c r="C142" s="32"/>
+      <c r="D142" s="29"/>
+      <c r="E142" s="42"/>
+      <c r="F142" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="8"/>
-      <c r="B143" s="11"/>
-      <c r="C143" s="37"/>
-      <c r="D143" s="38"/>
-      <c r="E143" s="90"/>
-      <c r="F143" s="39">
+      <c r="B143" s="10"/>
+      <c r="C143" s="32"/>
+      <c r="D143" s="33"/>
+      <c r="E143" s="42"/>
+      <c r="F143" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="12"/>
-      <c r="B144" s="13"/>
-      <c r="C144" s="14"/>
-      <c r="D144" s="74" t="s">
+      <c r="A144" s="11"/>
+      <c r="B144" s="12"/>
+      <c r="C144" s="13"/>
+      <c r="D144" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="E144" s="75"/>
+      <c r="E144" s="78"/>
       <c r="F144" s="9">
         <f>SUM(F9:F143)</f>
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="84" t="s">
+      <c r="A145" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="B145" s="85"/>
-      <c r="C145" s="85"/>
-      <c r="D145" s="85"/>
-      <c r="E145" s="85"/>
-      <c r="F145" s="86"/>
+      <c r="B145" s="88"/>
+      <c r="C145" s="88"/>
+      <c r="D145" s="88"/>
+      <c r="E145" s="88"/>
+      <c r="F145" s="89"/>
     </row>
     <row r="146" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A146" s="76"/>
-      <c r="B146" s="77"/>
-      <c r="C146" s="77"/>
-      <c r="D146" s="77"/>
-      <c r="E146" s="77"/>
-      <c r="F146" s="78"/>
+      <c r="A146" s="79"/>
+      <c r="B146" s="80"/>
+      <c r="C146" s="80"/>
+      <c r="D146" s="80"/>
+      <c r="E146" s="80"/>
+      <c r="F146" s="81"/>
     </row>
     <row r="147" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="79" t="s">
+      <c r="A147" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B147" s="80"/>
-      <c r="C147" s="81"/>
-      <c r="D147" s="82" t="s">
+      <c r="B147" s="83"/>
+      <c r="C147" s="84"/>
+      <c r="D147" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="E147" s="82"/>
-      <c r="F147" s="83"/>
+      <c r="E147" s="85"/>
+      <c r="F147" s="86"/>
     </row>
     <row r="148" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B148" s="15"/>
-      <c r="C148" s="21"/>
-      <c r="D148" s="67"/>
-      <c r="E148" s="68"/>
-      <c r="F148" s="69"/>
+      <c r="B148" s="14"/>
+      <c r="C148" s="20"/>
+      <c r="D148" s="70"/>
+      <c r="E148" s="71"/>
+      <c r="F148" s="72"/>
     </row>
     <row r="149" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B149" s="15"/>
-      <c r="C149" s="16"/>
-      <c r="D149" s="70"/>
-      <c r="E149" s="70"/>
-      <c r="F149" s="71"/>
+      <c r="B149" s="14"/>
+      <c r="C149" s="15"/>
+      <c r="D149" s="73"/>
+      <c r="E149" s="73"/>
+      <c r="F149" s="74"/>
     </row>
     <row r="150" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="17" t="s">
+      <c r="A150" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B150" s="18"/>
-      <c r="C150" s="22"/>
-      <c r="D150" s="72" t="s">
+      <c r="B150" s="17"/>
+      <c r="C150" s="21"/>
+      <c r="D150" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="E150" s="72"/>
-      <c r="F150" s="73"/>
-      <c r="G150" s="44" t="s">
+      <c r="E150" s="75"/>
+      <c r="F150" s="76"/>
+      <c r="G150" s="38" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="6"/>
-      <c r="B151" s="19"/>
-      <c r="C151" s="20"/>
-      <c r="D151" s="19"/>
-      <c r="E151" s="19"/>
-      <c r="F151" s="20"/>
-      <c r="G151" s="44" t="s">
+      <c r="B151" s="18"/>
+      <c r="C151" s="19"/>
+      <c r="D151" s="18"/>
+      <c r="E151" s="18"/>
+      <c r="F151" s="19"/>
+      <c r="G151" s="38" t="s">
         <v>25</v>
       </c>
     </row>

--- a/backend/templates/pr-template 4p.xlsx
+++ b/backend/templates/pr-template 4p.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8C8438-20E8-42C1-830C-D57170D6D199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C603A94-6AA7-427F-ADCD-7A38BAA0C3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -540,6 +540,113 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -557,113 +664,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1077,6 +1077,7 @@
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="6" width="13.54296875" customWidth="1"/>
     <col min="7" max="7" width="5.453125" customWidth="1"/>
+    <col min="12" max="12" width="35.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1084,26 +1085,26 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="57"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="72"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="60"/>
+      <c r="A2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="75"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="61"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="63"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="78"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1111,68 +1112,68 @@
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="26"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="65"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="80"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="67"/>
+      <c r="B5" s="82"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="69"/>
+      <c r="F5" s="84"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="50"/>
-      <c r="B6" s="51"/>
+      <c r="A6" s="87"/>
+      <c r="B6" s="88"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="49"/>
+      <c r="F6" s="86"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D7" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="54" t="s">
+      <c r="E7" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="54" t="s">
+      <c r="F7" s="56" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="53"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
+      <c r="A8" s="90"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="37"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="90"/>
+      <c r="C9" s="48"/>
       <c r="D9" s="36"/>
       <c r="E9" s="39"/>
       <c r="F9" s="34">
@@ -1183,7 +1184,7 @@
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="37"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="90"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="36"/>
       <c r="E10" s="39"/>
       <c r="F10" s="34">
@@ -1194,7 +1195,7 @@
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="37"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="90"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="36"/>
       <c r="E11" s="39"/>
       <c r="F11" s="34">
@@ -1205,7 +1206,7 @@
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="37"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="90"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="36"/>
       <c r="E12" s="39"/>
       <c r="F12" s="34">
@@ -1216,7 +1217,7 @@
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="37"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="90"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="36"/>
       <c r="E13" s="39"/>
       <c r="F13" s="34">
@@ -1227,7 +1228,7 @@
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="37"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="90"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="36"/>
       <c r="E14" s="39"/>
       <c r="F14" s="34">
@@ -1238,7 +1239,7 @@
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="37"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="90"/>
+      <c r="C15" s="48"/>
       <c r="D15" s="36"/>
       <c r="E15" s="39"/>
       <c r="F15" s="34">
@@ -1249,7 +1250,7 @@
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="37"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="90"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="36"/>
       <c r="E16" s="39"/>
       <c r="F16" s="34">
@@ -1260,7 +1261,7 @@
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="37"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="90"/>
+      <c r="C17" s="48"/>
       <c r="D17" s="36"/>
       <c r="E17" s="39"/>
       <c r="F17" s="34">
@@ -1271,7 +1272,7 @@
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="37"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="90"/>
+      <c r="C18" s="48"/>
       <c r="D18" s="36"/>
       <c r="E18" s="39"/>
       <c r="F18" s="34">
@@ -1282,7 +1283,7 @@
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="37"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="90"/>
+      <c r="C19" s="48"/>
       <c r="D19" s="36"/>
       <c r="E19" s="39"/>
       <c r="F19" s="34">
@@ -1293,7 +1294,7 @@
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="37"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="90"/>
+      <c r="C20" s="48"/>
       <c r="D20" s="36"/>
       <c r="E20" s="39"/>
       <c r="F20" s="34">
@@ -1304,7 +1305,7 @@
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="37"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="90"/>
+      <c r="C21" s="48"/>
       <c r="D21" s="36"/>
       <c r="E21" s="39"/>
       <c r="F21" s="34">
@@ -1315,7 +1316,7 @@
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="37"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="90"/>
+      <c r="C22" s="48"/>
       <c r="D22" s="36"/>
       <c r="E22" s="39"/>
       <c r="F22" s="34">
@@ -1326,7 +1327,7 @@
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="37"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="90"/>
+      <c r="C23" s="48"/>
       <c r="D23" s="36"/>
       <c r="E23" s="39"/>
       <c r="F23" s="34">
@@ -1337,7 +1338,7 @@
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="37"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="90"/>
+      <c r="C24" s="48"/>
       <c r="D24" s="36"/>
       <c r="E24" s="39"/>
       <c r="F24" s="34">
@@ -1348,7 +1349,7 @@
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="37"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="90"/>
+      <c r="C25" s="48"/>
       <c r="D25" s="36"/>
       <c r="E25" s="39"/>
       <c r="F25" s="34">
@@ -1359,7 +1360,7 @@
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="37"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="90"/>
+      <c r="C26" s="48"/>
       <c r="D26" s="36"/>
       <c r="E26" s="39"/>
       <c r="F26" s="34">
@@ -1370,7 +1371,7 @@
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="37"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="90"/>
+      <c r="C27" s="48"/>
       <c r="D27" s="36"/>
       <c r="E27" s="39"/>
       <c r="F27" s="34">
@@ -1381,7 +1382,7 @@
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="37"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="90"/>
+      <c r="C28" s="48"/>
       <c r="D28" s="36"/>
       <c r="E28" s="39"/>
       <c r="F28" s="34">
@@ -1392,7 +1393,7 @@
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="37"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="90"/>
+      <c r="C29" s="48"/>
       <c r="D29" s="36"/>
       <c r="E29" s="39"/>
       <c r="F29" s="34">
@@ -1403,7 +1404,7 @@
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="37"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="90"/>
+      <c r="C30" s="48"/>
       <c r="D30" s="36"/>
       <c r="E30" s="39"/>
       <c r="F30" s="34">
@@ -1414,7 +1415,7 @@
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="37"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="90"/>
+      <c r="C31" s="48"/>
       <c r="D31" s="36"/>
       <c r="E31" s="39"/>
       <c r="F31" s="34">
@@ -1425,7 +1426,7 @@
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="37"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="90"/>
+      <c r="C32" s="48"/>
       <c r="D32" s="36"/>
       <c r="E32" s="39"/>
       <c r="F32" s="34">
@@ -1436,7 +1437,7 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="37"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="90"/>
+      <c r="C33" s="48"/>
       <c r="D33" s="36"/>
       <c r="E33" s="39"/>
       <c r="F33" s="34">
@@ -1447,7 +1448,7 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="37"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="90"/>
+      <c r="C34" s="48"/>
       <c r="D34" s="36"/>
       <c r="E34" s="39"/>
       <c r="F34" s="34">
@@ -1458,7 +1459,7 @@
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="37"/>
       <c r="B35" s="27"/>
-      <c r="C35" s="90"/>
+      <c r="C35" s="48"/>
       <c r="D35" s="36"/>
       <c r="E35" s="39"/>
       <c r="F35" s="34">
@@ -1469,7 +1470,7 @@
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="37"/>
       <c r="B36" s="27"/>
-      <c r="C36" s="90"/>
+      <c r="C36" s="48"/>
       <c r="D36" s="36"/>
       <c r="E36" s="39"/>
       <c r="F36" s="34">
@@ -1480,7 +1481,7 @@
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="37"/>
       <c r="B37" s="27"/>
-      <c r="C37" s="90"/>
+      <c r="C37" s="48"/>
       <c r="D37" s="36"/>
       <c r="E37" s="39"/>
       <c r="F37" s="34">
@@ -1491,7 +1492,7 @@
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="37"/>
       <c r="B38" s="27"/>
-      <c r="C38" s="90"/>
+      <c r="C38" s="48"/>
       <c r="D38" s="36"/>
       <c r="E38" s="39"/>
       <c r="F38" s="34">
@@ -1502,7 +1503,7 @@
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="37"/>
       <c r="B39" s="27"/>
-      <c r="C39" s="90"/>
+      <c r="C39" s="48"/>
       <c r="D39" s="36"/>
       <c r="E39" s="39"/>
       <c r="F39" s="34">
@@ -1516,7 +1517,7 @@
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="37"/>
       <c r="B40" s="27"/>
-      <c r="C40" s="90"/>
+      <c r="C40" s="48"/>
       <c r="D40" s="36"/>
       <c r="E40" s="39"/>
       <c r="F40" s="34">
@@ -1530,7 +1531,7 @@
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="37"/>
       <c r="B41" s="27"/>
-      <c r="C41" s="90"/>
+      <c r="C41" s="48"/>
       <c r="D41" s="36"/>
       <c r="E41" s="39"/>
       <c r="F41" s="34">
@@ -1541,7 +1542,7 @@
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="37"/>
       <c r="B42" s="27"/>
-      <c r="C42" s="90"/>
+      <c r="C42" s="48"/>
       <c r="D42" s="36"/>
       <c r="E42" s="39"/>
       <c r="F42" s="34">
@@ -1552,7 +1553,7 @@
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="37"/>
       <c r="B43" s="27"/>
-      <c r="C43" s="90"/>
+      <c r="C43" s="48"/>
       <c r="D43" s="36"/>
       <c r="E43" s="39"/>
       <c r="F43" s="34">
@@ -1563,7 +1564,7 @@
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="37"/>
       <c r="B44" s="27"/>
-      <c r="C44" s="90"/>
+      <c r="C44" s="48"/>
       <c r="D44" s="36"/>
       <c r="E44" s="39"/>
       <c r="F44" s="34">
@@ -1574,7 +1575,7 @@
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="37"/>
       <c r="B45" s="27"/>
-      <c r="C45" s="90"/>
+      <c r="C45" s="48"/>
       <c r="D45" s="36"/>
       <c r="E45" s="39"/>
       <c r="F45" s="34">
@@ -1585,7 +1586,7 @@
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="37"/>
       <c r="B46" s="27"/>
-      <c r="C46" s="90"/>
+      <c r="C46" s="48"/>
       <c r="D46" s="36"/>
       <c r="E46" s="39"/>
       <c r="F46" s="34">
@@ -1596,7 +1597,7 @@
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="37"/>
       <c r="B47" s="27"/>
-      <c r="C47" s="90"/>
+      <c r="C47" s="48"/>
       <c r="D47" s="36"/>
       <c r="E47" s="39"/>
       <c r="F47" s="34">
@@ -1607,7 +1608,7 @@
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="37"/>
       <c r="B48" s="27"/>
-      <c r="C48" s="90"/>
+      <c r="C48" s="48"/>
       <c r="D48" s="36"/>
       <c r="E48" s="39"/>
       <c r="F48" s="34">
@@ -1618,7 +1619,7 @@
     <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="37"/>
       <c r="B49" s="27"/>
-      <c r="C49" s="90"/>
+      <c r="C49" s="48"/>
       <c r="D49" s="36"/>
       <c r="E49" s="39"/>
       <c r="F49" s="34">
@@ -1629,7 +1630,7 @@
     <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="37"/>
       <c r="B50" s="27"/>
-      <c r="C50" s="90"/>
+      <c r="C50" s="48"/>
       <c r="D50" s="36"/>
       <c r="E50" s="39"/>
       <c r="F50" s="34">
@@ -1640,7 +1641,7 @@
     <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="37"/>
       <c r="B51" s="27"/>
-      <c r="C51" s="90"/>
+      <c r="C51" s="48"/>
       <c r="D51" s="36"/>
       <c r="E51" s="39"/>
       <c r="F51" s="34">
@@ -1651,7 +1652,7 @@
     <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="37"/>
       <c r="B52" s="27"/>
-      <c r="C52" s="90"/>
+      <c r="C52" s="48"/>
       <c r="D52" s="36"/>
       <c r="E52" s="39"/>
       <c r="F52" s="34">
@@ -1662,7 +1663,7 @@
     <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="37"/>
       <c r="B53" s="27"/>
-      <c r="C53" s="90"/>
+      <c r="C53" s="48"/>
       <c r="D53" s="36"/>
       <c r="E53" s="39"/>
       <c r="F53" s="34">
@@ -1673,7 +1674,7 @@
     <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="37"/>
       <c r="B54" s="27"/>
-      <c r="C54" s="90"/>
+      <c r="C54" s="48"/>
       <c r="D54" s="36"/>
       <c r="E54" s="39"/>
       <c r="F54" s="34">
@@ -1684,7 +1685,7 @@
     <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="37"/>
       <c r="B55" s="27"/>
-      <c r="C55" s="90"/>
+      <c r="C55" s="48"/>
       <c r="D55" s="36"/>
       <c r="E55" s="39"/>
       <c r="F55" s="34">
@@ -1695,7 +1696,7 @@
     <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="37"/>
       <c r="B56" s="27"/>
-      <c r="C56" s="90"/>
+      <c r="C56" s="48"/>
       <c r="D56" s="36"/>
       <c r="E56" s="39"/>
       <c r="F56" s="34">
@@ -1706,7 +1707,7 @@
     <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="37"/>
       <c r="B57" s="27"/>
-      <c r="C57" s="90"/>
+      <c r="C57" s="48"/>
       <c r="D57" s="36"/>
       <c r="E57" s="39"/>
       <c r="F57" s="34">
@@ -1717,7 +1718,7 @@
     <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="37"/>
       <c r="B58" s="27"/>
-      <c r="C58" s="90"/>
+      <c r="C58" s="48"/>
       <c r="D58" s="36"/>
       <c r="E58" s="39"/>
       <c r="F58" s="34">
@@ -1728,7 +1729,7 @@
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="37"/>
       <c r="B59" s="27"/>
-      <c r="C59" s="90"/>
+      <c r="C59" s="48"/>
       <c r="D59" s="36"/>
       <c r="E59" s="39"/>
       <c r="F59" s="34">
@@ -1739,7 +1740,7 @@
     <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="37"/>
       <c r="B60" s="27"/>
-      <c r="C60" s="90"/>
+      <c r="C60" s="48"/>
       <c r="D60" s="36"/>
       <c r="E60" s="39"/>
       <c r="F60" s="34">
@@ -1750,7 +1751,7 @@
     <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="37"/>
       <c r="B61" s="27"/>
-      <c r="C61" s="90"/>
+      <c r="C61" s="48"/>
       <c r="D61" s="36"/>
       <c r="E61" s="39"/>
       <c r="F61" s="34">
@@ -1761,7 +1762,7 @@
     <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="37"/>
       <c r="B62" s="27"/>
-      <c r="C62" s="90"/>
+      <c r="C62" s="48"/>
       <c r="D62" s="36"/>
       <c r="E62" s="39"/>
       <c r="F62" s="34">
@@ -1772,7 +1773,7 @@
     <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="37"/>
       <c r="B63" s="27"/>
-      <c r="C63" s="90"/>
+      <c r="C63" s="48"/>
       <c r="D63" s="36"/>
       <c r="E63" s="39"/>
       <c r="F63" s="34">
@@ -1783,7 +1784,7 @@
     <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="37"/>
       <c r="B64" s="27"/>
-      <c r="C64" s="90"/>
+      <c r="C64" s="48"/>
       <c r="D64" s="36"/>
       <c r="E64" s="39"/>
       <c r="F64" s="34">
@@ -1794,7 +1795,7 @@
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="37"/>
       <c r="B65" s="27"/>
-      <c r="C65" s="90"/>
+      <c r="C65" s="48"/>
       <c r="D65" s="36"/>
       <c r="E65" s="39"/>
       <c r="F65" s="34">
@@ -1805,7 +1806,7 @@
     <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="37"/>
       <c r="B66" s="27"/>
-      <c r="C66" s="90"/>
+      <c r="C66" s="48"/>
       <c r="D66" s="36"/>
       <c r="E66" s="39"/>
       <c r="F66" s="34">
@@ -1816,7 +1817,7 @@
     <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="37"/>
       <c r="B67" s="27"/>
-      <c r="C67" s="90"/>
+      <c r="C67" s="48"/>
       <c r="D67" s="36"/>
       <c r="E67" s="39"/>
       <c r="F67" s="34">
@@ -1827,7 +1828,7 @@
     <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="37"/>
       <c r="B68" s="27"/>
-      <c r="C68" s="90"/>
+      <c r="C68" s="48"/>
       <c r="D68" s="36"/>
       <c r="E68" s="39"/>
       <c r="F68" s="34">
@@ -1838,7 +1839,7 @@
     <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="37"/>
       <c r="B69" s="27"/>
-      <c r="C69" s="90"/>
+      <c r="C69" s="48"/>
       <c r="D69" s="36"/>
       <c r="E69" s="39"/>
       <c r="F69" s="34">
@@ -1849,7 +1850,7 @@
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="37"/>
       <c r="B70" s="27"/>
-      <c r="C70" s="90"/>
+      <c r="C70" s="48"/>
       <c r="D70" s="36"/>
       <c r="E70" s="39"/>
       <c r="F70" s="34">
@@ -1860,7 +1861,7 @@
     <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="37"/>
       <c r="B71" s="27"/>
-      <c r="C71" s="90"/>
+      <c r="C71" s="48"/>
       <c r="D71" s="36"/>
       <c r="E71" s="39"/>
       <c r="F71" s="34">
@@ -1871,7 +1872,7 @@
     <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="37"/>
       <c r="B72" s="27"/>
-      <c r="C72" s="90"/>
+      <c r="C72" s="48"/>
       <c r="D72" s="36"/>
       <c r="E72" s="39"/>
       <c r="F72" s="34">
@@ -1882,7 +1883,7 @@
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="37"/>
       <c r="B73" s="27"/>
-      <c r="C73" s="90"/>
+      <c r="C73" s="48"/>
       <c r="D73" s="36"/>
       <c r="E73" s="39"/>
       <c r="F73" s="34">
@@ -1893,7 +1894,7 @@
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="37"/>
       <c r="B74" s="27"/>
-      <c r="C74" s="90"/>
+      <c r="C74" s="48"/>
       <c r="D74" s="36"/>
       <c r="E74" s="39"/>
       <c r="F74" s="34">
@@ -1904,7 +1905,7 @@
     <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="37"/>
       <c r="B75" s="27"/>
-      <c r="C75" s="90"/>
+      <c r="C75" s="48"/>
       <c r="D75" s="36"/>
       <c r="E75" s="39"/>
       <c r="F75" s="34">
@@ -1915,7 +1916,7 @@
     <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="37"/>
       <c r="B76" s="27"/>
-      <c r="C76" s="90"/>
+      <c r="C76" s="48"/>
       <c r="D76" s="36"/>
       <c r="E76" s="39"/>
       <c r="F76" s="34">
@@ -1926,7 +1927,7 @@
     <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="37"/>
       <c r="B77" s="27"/>
-      <c r="C77" s="90"/>
+      <c r="C77" s="48"/>
       <c r="D77" s="36"/>
       <c r="E77" s="39"/>
       <c r="F77" s="34">
@@ -1937,7 +1938,7 @@
     <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="37"/>
       <c r="B78" s="27"/>
-      <c r="C78" s="90"/>
+      <c r="C78" s="48"/>
       <c r="D78" s="36"/>
       <c r="E78" s="39"/>
       <c r="F78" s="34">
@@ -1948,7 +1949,7 @@
     <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="37"/>
       <c r="B79" s="27"/>
-      <c r="C79" s="90"/>
+      <c r="C79" s="48"/>
       <c r="D79" s="36"/>
       <c r="E79" s="39"/>
       <c r="F79" s="34">
@@ -1959,7 +1960,7 @@
     <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="37"/>
       <c r="B80" s="27"/>
-      <c r="C80" s="90"/>
+      <c r="C80" s="48"/>
       <c r="D80" s="36"/>
       <c r="E80" s="39"/>
       <c r="F80" s="34">
@@ -1973,7 +1974,7 @@
     <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="37"/>
       <c r="B81" s="27"/>
-      <c r="C81" s="90"/>
+      <c r="C81" s="48"/>
       <c r="D81" s="36"/>
       <c r="E81" s="39"/>
       <c r="F81" s="34">
@@ -1987,7 +1988,7 @@
     <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="37"/>
       <c r="B82" s="27"/>
-      <c r="C82" s="90"/>
+      <c r="C82" s="48"/>
       <c r="D82" s="36"/>
       <c r="E82" s="39"/>
       <c r="F82" s="34">
@@ -1998,7 +1999,7 @@
     <row r="83" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="37"/>
       <c r="B83" s="27"/>
-      <c r="C83" s="90"/>
+      <c r="C83" s="48"/>
       <c r="D83" s="36"/>
       <c r="E83" s="39"/>
       <c r="F83" s="34">
@@ -2009,7 +2010,7 @@
     <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="37"/>
       <c r="B84" s="27"/>
-      <c r="C84" s="90"/>
+      <c r="C84" s="48"/>
       <c r="D84" s="36"/>
       <c r="E84" s="39"/>
       <c r="F84" s="34">
@@ -2020,7 +2021,7 @@
     <row r="85" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="37"/>
       <c r="B85" s="27"/>
-      <c r="C85" s="90"/>
+      <c r="C85" s="48"/>
       <c r="D85" s="36"/>
       <c r="E85" s="39"/>
       <c r="F85" s="34">
@@ -2031,7 +2032,7 @@
     <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="37"/>
       <c r="B86" s="27"/>
-      <c r="C86" s="90"/>
+      <c r="C86" s="48"/>
       <c r="D86" s="36"/>
       <c r="E86" s="39"/>
       <c r="F86" s="34">
@@ -2042,7 +2043,7 @@
     <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="37"/>
       <c r="B87" s="27"/>
-      <c r="C87" s="90"/>
+      <c r="C87" s="48"/>
       <c r="D87" s="36"/>
       <c r="E87" s="39"/>
       <c r="F87" s="34">
@@ -2053,7 +2054,7 @@
     <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="37"/>
       <c r="B88" s="27"/>
-      <c r="C88" s="90"/>
+      <c r="C88" s="48"/>
       <c r="D88" s="36"/>
       <c r="E88" s="39"/>
       <c r="F88" s="34">
@@ -2064,7 +2065,7 @@
     <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="37"/>
       <c r="B89" s="27"/>
-      <c r="C89" s="90"/>
+      <c r="C89" s="48"/>
       <c r="D89" s="36"/>
       <c r="E89" s="39"/>
       <c r="F89" s="34">
@@ -2075,7 +2076,7 @@
     <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="37"/>
       <c r="B90" s="27"/>
-      <c r="C90" s="90"/>
+      <c r="C90" s="48"/>
       <c r="D90" s="36"/>
       <c r="E90" s="39"/>
       <c r="F90" s="34">
@@ -2086,7 +2087,7 @@
     <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="37"/>
       <c r="B91" s="27"/>
-      <c r="C91" s="90"/>
+      <c r="C91" s="48"/>
       <c r="D91" s="36"/>
       <c r="E91" s="39"/>
       <c r="F91" s="34">
@@ -2097,7 +2098,7 @@
     <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="37"/>
       <c r="B92" s="27"/>
-      <c r="C92" s="90"/>
+      <c r="C92" s="48"/>
       <c r="D92" s="36"/>
       <c r="E92" s="39"/>
       <c r="F92" s="34">
@@ -2108,7 +2109,7 @@
     <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="37"/>
       <c r="B93" s="27"/>
-      <c r="C93" s="90"/>
+      <c r="C93" s="48"/>
       <c r="D93" s="36"/>
       <c r="E93" s="39"/>
       <c r="F93" s="34">
@@ -2119,7 +2120,7 @@
     <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="37"/>
       <c r="B94" s="27"/>
-      <c r="C94" s="90"/>
+      <c r="C94" s="48"/>
       <c r="D94" s="36"/>
       <c r="E94" s="39"/>
       <c r="F94" s="34">
@@ -2130,7 +2131,7 @@
     <row r="95" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="37"/>
       <c r="B95" s="27"/>
-      <c r="C95" s="90"/>
+      <c r="C95" s="48"/>
       <c r="D95" s="36"/>
       <c r="E95" s="39"/>
       <c r="F95" s="34">
@@ -2141,7 +2142,7 @@
     <row r="96" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="37"/>
       <c r="B96" s="27"/>
-      <c r="C96" s="90"/>
+      <c r="C96" s="48"/>
       <c r="D96" s="36"/>
       <c r="E96" s="39"/>
       <c r="F96" s="34">
@@ -2152,7 +2153,7 @@
     <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="37"/>
       <c r="B97" s="27"/>
-      <c r="C97" s="90"/>
+      <c r="C97" s="48"/>
       <c r="D97" s="36"/>
       <c r="E97" s="39"/>
       <c r="F97" s="34">
@@ -2163,7 +2164,7 @@
     <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="37"/>
       <c r="B98" s="27"/>
-      <c r="C98" s="90"/>
+      <c r="C98" s="48"/>
       <c r="D98" s="36"/>
       <c r="E98" s="39"/>
       <c r="F98" s="34">
@@ -2174,7 +2175,7 @@
     <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="37"/>
       <c r="B99" s="27"/>
-      <c r="C99" s="90"/>
+      <c r="C99" s="48"/>
       <c r="D99" s="36"/>
       <c r="E99" s="39"/>
       <c r="F99" s="34">
@@ -2185,7 +2186,7 @@
     <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="37"/>
       <c r="B100" s="27"/>
-      <c r="C100" s="90"/>
+      <c r="C100" s="48"/>
       <c r="D100" s="36"/>
       <c r="E100" s="39"/>
       <c r="F100" s="34">
@@ -2196,7 +2197,7 @@
     <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="37"/>
       <c r="B101" s="27"/>
-      <c r="C101" s="90"/>
+      <c r="C101" s="48"/>
       <c r="D101" s="36"/>
       <c r="E101" s="39"/>
       <c r="F101" s="34">
@@ -2207,7 +2208,7 @@
     <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="37"/>
       <c r="B102" s="27"/>
-      <c r="C102" s="90"/>
+      <c r="C102" s="48"/>
       <c r="D102" s="36"/>
       <c r="E102" s="39"/>
       <c r="F102" s="34">
@@ -2218,7 +2219,7 @@
     <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="37"/>
       <c r="B103" s="27"/>
-      <c r="C103" s="90"/>
+      <c r="C103" s="48"/>
       <c r="D103" s="36"/>
       <c r="E103" s="39"/>
       <c r="F103" s="34">
@@ -2229,7 +2230,7 @@
     <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="37"/>
       <c r="B104" s="27"/>
-      <c r="C104" s="90"/>
+      <c r="C104" s="48"/>
       <c r="D104" s="36"/>
       <c r="E104" s="39"/>
       <c r="F104" s="34">
@@ -2240,7 +2241,7 @@
     <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="37"/>
       <c r="B105" s="27"/>
-      <c r="C105" s="90"/>
+      <c r="C105" s="48"/>
       <c r="D105" s="36"/>
       <c r="E105" s="39"/>
       <c r="F105" s="34">
@@ -2251,7 +2252,7 @@
     <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="37"/>
       <c r="B106" s="27"/>
-      <c r="C106" s="90"/>
+      <c r="C106" s="48"/>
       <c r="D106" s="36"/>
       <c r="E106" s="39"/>
       <c r="F106" s="34">
@@ -2262,7 +2263,7 @@
     <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="37"/>
       <c r="B107" s="27"/>
-      <c r="C107" s="90"/>
+      <c r="C107" s="48"/>
       <c r="D107" s="36"/>
       <c r="E107" s="39"/>
       <c r="F107" s="34">
@@ -2273,7 +2274,7 @@
     <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="37"/>
       <c r="B108" s="27"/>
-      <c r="C108" s="90"/>
+      <c r="C108" s="48"/>
       <c r="D108" s="36"/>
       <c r="E108" s="39"/>
       <c r="F108" s="34">
@@ -2284,7 +2285,7 @@
     <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="37"/>
       <c r="B109" s="27"/>
-      <c r="C109" s="90"/>
+      <c r="C109" s="48"/>
       <c r="D109" s="36"/>
       <c r="E109" s="39"/>
       <c r="F109" s="34">
@@ -2295,7 +2296,7 @@
     <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="37"/>
       <c r="B110" s="27"/>
-      <c r="C110" s="90"/>
+      <c r="C110" s="48"/>
       <c r="D110" s="36"/>
       <c r="E110" s="39"/>
       <c r="F110" s="34">
@@ -2306,7 +2307,7 @@
     <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="37"/>
       <c r="B111" s="27"/>
-      <c r="C111" s="90"/>
+      <c r="C111" s="48"/>
       <c r="D111" s="36"/>
       <c r="E111" s="39"/>
       <c r="F111" s="34">
@@ -2317,7 +2318,7 @@
     <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="37"/>
       <c r="B112" s="27"/>
-      <c r="C112" s="90"/>
+      <c r="C112" s="48"/>
       <c r="D112" s="36"/>
       <c r="E112" s="39"/>
       <c r="F112" s="34">
@@ -2328,7 +2329,7 @@
     <row r="113" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="37"/>
       <c r="B113" s="27"/>
-      <c r="C113" s="90"/>
+      <c r="C113" s="48"/>
       <c r="D113" s="36"/>
       <c r="E113" s="39"/>
       <c r="F113" s="34">
@@ -2339,7 +2340,7 @@
     <row r="114" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="37"/>
       <c r="B114" s="27"/>
-      <c r="C114" s="90"/>
+      <c r="C114" s="48"/>
       <c r="D114" s="36"/>
       <c r="E114" s="39"/>
       <c r="F114" s="34">
@@ -2350,7 +2351,7 @@
     <row r="115" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="37"/>
       <c r="B115" s="27"/>
-      <c r="C115" s="90"/>
+      <c r="C115" s="48"/>
       <c r="D115" s="36"/>
       <c r="E115" s="39"/>
       <c r="F115" s="34">
@@ -2361,7 +2362,7 @@
     <row r="116" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="37"/>
       <c r="B116" s="27"/>
-      <c r="C116" s="90"/>
+      <c r="C116" s="48"/>
       <c r="D116" s="36"/>
       <c r="E116" s="39"/>
       <c r="F116" s="34">
@@ -2372,7 +2373,7 @@
     <row r="117" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="37"/>
       <c r="B117" s="27"/>
-      <c r="C117" s="90"/>
+      <c r="C117" s="48"/>
       <c r="D117" s="36"/>
       <c r="E117" s="39"/>
       <c r="F117" s="34">
@@ -2676,44 +2677,44 @@
       <c r="A144" s="11"/>
       <c r="B144" s="12"/>
       <c r="C144" s="13"/>
-      <c r="D144" s="77" t="s">
+      <c r="D144" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="E144" s="78"/>
+      <c r="E144" s="59"/>
       <c r="F144" s="9">
         <f>SUM(F9:F143)</f>
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="87" t="s">
+      <c r="A145" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="B145" s="88"/>
-      <c r="C145" s="88"/>
-      <c r="D145" s="88"/>
-      <c r="E145" s="88"/>
-      <c r="F145" s="89"/>
+      <c r="B145" s="69"/>
+      <c r="C145" s="69"/>
+      <c r="D145" s="69"/>
+      <c r="E145" s="69"/>
+      <c r="F145" s="70"/>
     </row>
     <row r="146" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A146" s="79"/>
-      <c r="B146" s="80"/>
-      <c r="C146" s="80"/>
-      <c r="D146" s="80"/>
-      <c r="E146" s="80"/>
-      <c r="F146" s="81"/>
+      <c r="A146" s="60"/>
+      <c r="B146" s="61"/>
+      <c r="C146" s="61"/>
+      <c r="D146" s="61"/>
+      <c r="E146" s="61"/>
+      <c r="F146" s="62"/>
     </row>
     <row r="147" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="82" t="s">
+      <c r="A147" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="B147" s="83"/>
-      <c r="C147" s="84"/>
-      <c r="D147" s="85" t="s">
+      <c r="B147" s="64"/>
+      <c r="C147" s="65"/>
+      <c r="D147" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E147" s="85"/>
-      <c r="F147" s="86"/>
+      <c r="E147" s="66"/>
+      <c r="F147" s="67"/>
     </row>
     <row r="148" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
@@ -2721,9 +2722,9 @@
       </c>
       <c r="B148" s="14"/>
       <c r="C148" s="20"/>
-      <c r="D148" s="70"/>
-      <c r="E148" s="71"/>
-      <c r="F148" s="72"/>
+      <c r="D148" s="49"/>
+      <c r="E148" s="50"/>
+      <c r="F148" s="51"/>
     </row>
     <row r="149" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
@@ -2731,9 +2732,9 @@
       </c>
       <c r="B149" s="14"/>
       <c r="C149" s="15"/>
-      <c r="D149" s="73"/>
-      <c r="E149" s="73"/>
-      <c r="F149" s="74"/>
+      <c r="D149" s="52"/>
+      <c r="E149" s="52"/>
+      <c r="F149" s="53"/>
     </row>
     <row r="150" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="16" t="s">
@@ -2741,11 +2742,11 @@
       </c>
       <c r="B150" s="17"/>
       <c r="C150" s="21"/>
-      <c r="D150" s="75" t="s">
+      <c r="D150" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="E150" s="75"/>
-      <c r="F150" s="76"/>
+      <c r="E150" s="54"/>
+      <c r="F150" s="55"/>
       <c r="G150" s="38" t="s">
         <v>21</v>
       </c>
@@ -2766,6 +2767,18 @@
     <sortCondition ref="K6:K131"/>
   </sortState>
   <mergeCells count="23">
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="D148:F148"/>
     <mergeCell ref="D149:F149"/>
     <mergeCell ref="D150:F150"/>
@@ -2777,18 +2790,6 @@
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="A145:B145"/>
     <mergeCell ref="C145:F145"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="1.7716535433070868" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/pr-template 4p.xlsx
+++ b/backend/templates/pr-template 4p.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B076B34-31A7-4D1C-A5DC-2E16CA1C47BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0222EF92-CF44-4149-A8EA-18EE646CCC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -508,6 +508,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
@@ -629,21 +644,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1048,7 +1048,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G170"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.54296875" customWidth="1"/>
@@ -1065,26 +1065,26 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="62"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="67"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="65"/>
+      <c r="A2" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="70"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="66"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="68"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="73"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1092,63 +1092,63 @@
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="23"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="70"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="75"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="72"/>
+      <c r="B5" s="77"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="74"/>
+      <c r="F5" s="79"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="77"/>
-      <c r="B6" s="78"/>
+      <c r="A6" s="82"/>
+      <c r="B6" s="83"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="75" t="s">
+      <c r="E6" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="76"/>
+      <c r="F6" s="81"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="79" t="s">
+      <c r="A7" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="46" t="s">
+      <c r="E7" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="46" t="s">
+      <c r="F7" s="51" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="80"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
+      <c r="A8" s="85"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="29"/>
@@ -1575,10 +1575,10 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="81"/>
-      <c r="B47" s="82"/>
-      <c r="C47" s="83"/>
-      <c r="D47" s="84"/>
+      <c r="A47" s="39"/>
+      <c r="B47" s="40"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="42"/>
       <c r="E47" s="34"/>
       <c r="F47" s="27">
         <f t="shared" si="0"/>
@@ -2109,10 +2109,10 @@
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A95" s="81"/>
-      <c r="B95" s="82"/>
-      <c r="C95" s="83"/>
-      <c r="D95" s="84"/>
+      <c r="A95" s="39"/>
+      <c r="B95" s="40"/>
+      <c r="C95" s="41"/>
+      <c r="D95" s="42"/>
       <c r="E95" s="34"/>
       <c r="F95" s="27">
         <f t="shared" si="2"/>
@@ -2368,7 +2368,7 @@
       <c r="D118" s="25"/>
       <c r="E118" s="32"/>
       <c r="F118" s="27">
-        <f t="shared" ref="F118:F149" si="3">D118*E118</f>
+        <f t="shared" ref="F118:F162" si="3">D118*E118</f>
         <v>0</v>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       <c r="B141" s="21"/>
       <c r="C141" s="36"/>
       <c r="D141" s="21"/>
-      <c r="E141" s="85"/>
+      <c r="E141" s="43"/>
       <c r="F141" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2706,17 +2706,19 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="G146" s="30"/>
     </row>
     <row r="147" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" s="8"/>
       <c r="B147" s="21"/>
-      <c r="C147" s="37"/>
+      <c r="C147" s="36"/>
       <c r="D147" s="26"/>
       <c r="E147" s="33"/>
       <c r="F147" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="G147" s="30"/>
     </row>
     <row r="148" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" s="8"/>
@@ -2728,6 +2730,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="G148" s="30"/>
     </row>
     <row r="149" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" s="8"/>
@@ -2739,99 +2742,252 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="10"/>
-      <c r="B150" s="11"/>
-      <c r="C150" s="12"/>
-      <c r="D150" s="48" t="s">
+      <c r="G149" s="30"/>
+    </row>
+    <row r="150" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A150" s="8"/>
+      <c r="B150" s="21"/>
+      <c r="C150" s="36"/>
+      <c r="D150" s="26"/>
+      <c r="E150" s="33"/>
+      <c r="F150" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G150" s="30"/>
+    </row>
+    <row r="151" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A151" s="8"/>
+      <c r="B151" s="21"/>
+      <c r="C151" s="36"/>
+      <c r="D151" s="26"/>
+      <c r="E151" s="33"/>
+      <c r="F151" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G151" s="30"/>
+    </row>
+    <row r="152" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A152" s="8"/>
+      <c r="B152" s="21"/>
+      <c r="C152" s="36"/>
+      <c r="D152" s="26"/>
+      <c r="E152" s="33"/>
+      <c r="F152" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G152" s="30"/>
+    </row>
+    <row r="153" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A153" s="8"/>
+      <c r="B153" s="21"/>
+      <c r="C153" s="36"/>
+      <c r="D153" s="26"/>
+      <c r="E153" s="33"/>
+      <c r="F153" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G153" s="30"/>
+    </row>
+    <row r="154" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A154" s="8"/>
+      <c r="B154" s="21"/>
+      <c r="C154" s="36"/>
+      <c r="D154" s="21"/>
+      <c r="E154" s="43"/>
+      <c r="F154" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G154" s="30"/>
+    </row>
+    <row r="155" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A155" s="8"/>
+      <c r="B155" s="21"/>
+      <c r="C155" s="36"/>
+      <c r="D155" s="26"/>
+      <c r="E155" s="33"/>
+      <c r="F155" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G155" s="30"/>
+    </row>
+    <row r="156" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A156" s="8"/>
+      <c r="B156" s="21"/>
+      <c r="C156" s="36"/>
+      <c r="D156" s="26"/>
+      <c r="E156" s="33"/>
+      <c r="F156" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G156" s="30"/>
+    </row>
+    <row r="157" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A157" s="8"/>
+      <c r="B157" s="21"/>
+      <c r="C157" s="36"/>
+      <c r="D157" s="26"/>
+      <c r="E157" s="33"/>
+      <c r="F157" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G157" s="30"/>
+    </row>
+    <row r="158" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A158" s="8"/>
+      <c r="B158" s="21"/>
+      <c r="C158" s="36"/>
+      <c r="D158" s="26"/>
+      <c r="E158" s="33"/>
+      <c r="F158" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G158" s="30"/>
+    </row>
+    <row r="159" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A159" s="8"/>
+      <c r="B159" s="21"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="26"/>
+      <c r="E159" s="33"/>
+      <c r="F159" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A160" s="8"/>
+      <c r="B160" s="21"/>
+      <c r="C160" s="37"/>
+      <c r="D160" s="26"/>
+      <c r="E160" s="33"/>
+      <c r="F160" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A161" s="8"/>
+      <c r="B161" s="21"/>
+      <c r="C161" s="36"/>
+      <c r="D161" s="26"/>
+      <c r="E161" s="33"/>
+      <c r="F161" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A162" s="8"/>
+      <c r="B162" s="21"/>
+      <c r="C162" s="36"/>
+      <c r="D162" s="26"/>
+      <c r="E162" s="33"/>
+      <c r="F162" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="10"/>
+      <c r="B163" s="11"/>
+      <c r="C163" s="12"/>
+      <c r="D163" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="E150" s="49"/>
-      <c r="F150" s="9">
-        <f>SUM(F9:F149)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="58" t="s">
+      <c r="E163" s="54"/>
+      <c r="F163" s="9">
+        <f>SUM(F9:F162)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B151" s="59"/>
-      <c r="C151" s="59"/>
-      <c r="D151" s="59"/>
-      <c r="E151" s="59"/>
-      <c r="F151" s="60"/>
-    </row>
-    <row r="152" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A152" s="50"/>
-      <c r="B152" s="51"/>
-      <c r="C152" s="51"/>
-      <c r="D152" s="51"/>
-      <c r="E152" s="51"/>
-      <c r="F152" s="52"/>
-    </row>
-    <row r="153" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="53" t="s">
+      <c r="B164" s="64"/>
+      <c r="C164" s="64"/>
+      <c r="D164" s="64"/>
+      <c r="E164" s="64"/>
+      <c r="F164" s="65"/>
+    </row>
+    <row r="165" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A165" s="55"/>
+      <c r="B165" s="56"/>
+      <c r="C165" s="56"/>
+      <c r="D165" s="56"/>
+      <c r="E165" s="56"/>
+      <c r="F165" s="57"/>
+    </row>
+    <row r="166" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="B153" s="54"/>
-      <c r="C153" s="55"/>
-      <c r="D153" s="56" t="s">
+      <c r="B166" s="59"/>
+      <c r="C166" s="60"/>
+      <c r="D166" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="E153" s="56"/>
-      <c r="F153" s="57"/>
-    </row>
-    <row r="154" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="3" t="s">
+      <c r="E166" s="61"/>
+      <c r="F166" s="62"/>
+    </row>
+    <row r="167" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B154" s="13"/>
-      <c r="C154" s="19"/>
-      <c r="D154" s="39"/>
-      <c r="E154" s="40"/>
-      <c r="F154" s="41"/>
-    </row>
-    <row r="155" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="3" t="s">
+      <c r="B167" s="13"/>
+      <c r="C167" s="19"/>
+      <c r="D167" s="44"/>
+      <c r="E167" s="45"/>
+      <c r="F167" s="46"/>
+    </row>
+    <row r="168" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B155" s="13"/>
-      <c r="C155" s="14"/>
-      <c r="D155" s="42"/>
-      <c r="E155" s="42"/>
-      <c r="F155" s="43"/>
-    </row>
-    <row r="156" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="15" t="s">
+      <c r="B168" s="13"/>
+      <c r="C168" s="14"/>
+      <c r="D168" s="47"/>
+      <c r="E168" s="47"/>
+      <c r="F168" s="48"/>
+    </row>
+    <row r="169" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B156" s="16"/>
-      <c r="C156" s="20"/>
-      <c r="D156" s="44" t="s">
+      <c r="B169" s="16"/>
+      <c r="C169" s="20"/>
+      <c r="D169" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="E156" s="44"/>
-      <c r="F156" s="45"/>
-      <c r="G156" s="30" t="s">
+      <c r="E169" s="49"/>
+      <c r="F169" s="50"/>
+      <c r="G169" s="30" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A157" s="6"/>
-      <c r="B157" s="17"/>
-      <c r="C157" s="18"/>
-      <c r="D157" s="17"/>
-      <c r="E157" s="17"/>
-      <c r="F157" s="18"/>
-      <c r="G157" s="30" t="s">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A170" s="6"/>
+      <c r="B170" s="17"/>
+      <c r="C170" s="18"/>
+      <c r="D170" s="17"/>
+      <c r="E170" s="17"/>
+      <c r="F170" s="18"/>
+      <c r="G170" s="30" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K6:K149">
-    <sortCondition ref="K6:K149"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K6:K162">
+    <sortCondition ref="K6:K162"/>
   </sortState>
   <mergeCells count="23">
     <mergeCell ref="E6:F6"/>
@@ -2846,17 +3002,17 @@
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D155:F155"/>
-    <mergeCell ref="D156:F156"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D169:F169"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D150:E150"/>
-    <mergeCell ref="A152:F152"/>
-    <mergeCell ref="A153:C153"/>
-    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="D163:E163"/>
+    <mergeCell ref="A165:F165"/>
+    <mergeCell ref="A166:C166"/>
+    <mergeCell ref="D166:F166"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="A151:B151"/>
-    <mergeCell ref="C151:F151"/>
+    <mergeCell ref="A164:B164"/>
+    <mergeCell ref="C164:F164"/>
   </mergeCells>
   <pageMargins left="0.70866141732283461" right="0.51181102362204722" top="0.74803149606299213" bottom="1.7716535433070866" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="94" fitToHeight="0" orientation="portrait" r:id="rId1"/>
